--- a/research/traditional_assets/database/data/qatar/qatar_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/qatar/qatar_shipbuilding_marine.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0886794997776352</v>
+        <v>0.08863132027785758</v>
       </c>
       <c r="C2">
-        <v>3640.214686886517</v>
+        <v>3607.861314394231</v>
       </c>
       <c r="D2">
-        <v>3560.414686886517</v>
+        <v>3564.419676634726</v>
       </c>
       <c r="E2">
-        <v>-205.9362240495657</v>
+        <v>-169.57786180907</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>36.35836224049566</v>
       </c>
       <c r="G2">
         <v>79.8</v>
@@ -1451,28 +1451,28 @@
         <v>112.68</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.828825620696932</v>
       </c>
       <c r="N2">
-        <v>112.68</v>
+        <v>110.8511743793031</v>
       </c>
       <c r="O2">
-        <v>11.268</v>
+        <v>11.08511743793031</v>
       </c>
       <c r="P2">
-        <v>101.412</v>
+        <v>99.76605694137277</v>
       </c>
       <c r="Q2">
-        <v>211.812</v>
+        <v>210.1660569413728</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0886794997776352</v>
+        <v>0.08906931341197735</v>
       </c>
       <c r="T2">
-        <v>0.8594621135367391</v>
+        <v>0.8672754054779821</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>61.61331005252417</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08863132027785758</v>
+        <v>0.08858314077807994</v>
       </c>
       <c r="C3">
-        <v>3607.861314394231</v>
+        <v>3575.516962202896</v>
       </c>
       <c r="D3">
-        <v>3564.419676634726</v>
+        <v>3568.433686683887</v>
       </c>
       <c r="E3">
-        <v>-169.57786180907</v>
+        <v>-133.2194995685743</v>
       </c>
       <c r="F3">
-        <v>36.35836224049566</v>
+        <v>72.71672448099132</v>
       </c>
       <c r="G3">
         <v>79.8</v>
@@ -1533,28 +1533,28 @@
         <v>112.68</v>
       </c>
       <c r="M3">
-        <v>1.828825620696932</v>
+        <v>3.657651241393863</v>
       </c>
       <c r="N3">
-        <v>110.8511743793031</v>
+        <v>109.0223487586061</v>
       </c>
       <c r="O3">
-        <v>11.08511743793031</v>
+        <v>10.90223487586061</v>
       </c>
       <c r="P3">
-        <v>99.76605694137277</v>
+        <v>98.12011388274553</v>
       </c>
       <c r="Q3">
-        <v>210.1660569413728</v>
+        <v>208.5201138827455</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08906931341197735</v>
+        <v>0.08946708242661218</v>
       </c>
       <c r="T3">
-        <v>0.8672754054779821</v>
+        <v>0.8752481523568016</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>61.61331005252417</v>
+        <v>30.80665502626209</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08858314077807994</v>
+        <v>0.08853496127830229</v>
       </c>
       <c r="C4">
-        <v>3575.516962202896</v>
+        <v>3543.181660821037</v>
       </c>
       <c r="D4">
-        <v>3568.433686683887</v>
+        <v>3572.456747542524</v>
       </c>
       <c r="E4">
-        <v>-133.2194995685743</v>
+        <v>-96.86113732807871</v>
       </c>
       <c r="F4">
-        <v>72.71672448099132</v>
+        <v>109.075086721487</v>
       </c>
       <c r="G4">
         <v>79.8</v>
@@ -1615,28 +1615,28 @@
         <v>112.68</v>
       </c>
       <c r="M4">
-        <v>3.657651241393863</v>
+        <v>5.486476862090794</v>
       </c>
       <c r="N4">
-        <v>109.0223487586061</v>
+        <v>107.1935231379092</v>
       </c>
       <c r="O4">
-        <v>10.90223487586061</v>
+        <v>10.71935231379092</v>
       </c>
       <c r="P4">
-        <v>98.12011388274553</v>
+        <v>96.47417082411829</v>
       </c>
       <c r="Q4">
-        <v>208.5201138827455</v>
+        <v>206.8741708241183</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08946708242661218</v>
+        <v>0.08987305286422917</v>
       </c>
       <c r="T4">
-        <v>0.8752481523568016</v>
+        <v>0.8833852857692049</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>30.80665502626209</v>
+        <v>20.53777001750806</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08853496127830229</v>
+        <v>0.08848678177852466</v>
       </c>
       <c r="C5">
-        <v>3543.181660821037</v>
+        <v>3510.85544089492</v>
       </c>
       <c r="D5">
-        <v>3572.456747542524</v>
+        <v>3576.488889856902</v>
       </c>
       <c r="E5">
-        <v>-96.86113732807871</v>
+        <v>-60.50277508758305</v>
       </c>
       <c r="F5">
-        <v>109.075086721487</v>
+        <v>145.4334489619826</v>
       </c>
       <c r="G5">
         <v>79.8</v>
@@ -1697,28 +1697,28 @@
         <v>112.68</v>
       </c>
       <c r="M5">
-        <v>5.486476862090794</v>
+        <v>7.315302482787726</v>
       </c>
       <c r="N5">
-        <v>107.1935231379092</v>
+        <v>105.3646975172123</v>
       </c>
       <c r="O5">
-        <v>10.71935231379092</v>
+        <v>10.53646975172123</v>
       </c>
       <c r="P5">
-        <v>96.47417082411829</v>
+        <v>94.82822776549105</v>
       </c>
       <c r="Q5">
-        <v>206.8741708241183</v>
+        <v>205.2282277654911</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08987305286422917</v>
+        <v>0.09028748101929653</v>
       </c>
       <c r="T5">
-        <v>0.8833852857692049</v>
+        <v>0.8916919427943668</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>20.53777001750806</v>
+        <v>15.40332751313104</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08848678177852466</v>
+        <v>0.08850610227874703</v>
       </c>
       <c r="C6">
-        <v>3510.85544089492</v>
+        <v>3472.879053344112</v>
       </c>
       <c r="D6">
-        <v>3576.488889856902</v>
+        <v>3574.87086454659</v>
       </c>
       <c r="E6">
-        <v>-60.50277508758305</v>
+        <v>-24.14441284708738</v>
       </c>
       <c r="F6">
-        <v>145.4334489619826</v>
+        <v>181.7918112024783</v>
       </c>
       <c r="G6">
         <v>79.8</v>
@@ -1779,45 +1779,45 @@
         <v>112.68</v>
       </c>
       <c r="M6">
-        <v>7.315302482787726</v>
+        <v>9.416815820288376</v>
       </c>
       <c r="N6">
-        <v>105.3646975172123</v>
+        <v>103.2631841797116</v>
       </c>
       <c r="O6">
-        <v>10.53646975172123</v>
+        <v>10.32631841797116</v>
       </c>
       <c r="P6">
-        <v>94.82822776549105</v>
+        <v>92.93686576174046</v>
       </c>
       <c r="Q6">
-        <v>205.2282277654911</v>
+        <v>203.3368657617405</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09028748101929653</v>
+        <v>0.09071063397762845</v>
       </c>
       <c r="T6">
-        <v>0.8916919427943668</v>
+        <v>0.9001734768095319</v>
       </c>
       <c r="U6">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V6">
         <v>0.1</v>
       </c>
       <c r="W6">
-        <v>0.04527</v>
+        <v>0.04662</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y6">
-        <v>15.40332751313104</v>
+        <v>11.9658281685018</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08850610227874703</v>
+        <v>0.0884714227789694</v>
       </c>
       <c r="C7">
-        <v>3472.879053344112</v>
+        <v>3439.426025054966</v>
       </c>
       <c r="D7">
-        <v>3574.87086454659</v>
+        <v>3577.776198497939</v>
       </c>
       <c r="E7">
-        <v>-24.14441284708738</v>
+        <v>12.21394939340829</v>
       </c>
       <c r="F7">
-        <v>181.7918112024783</v>
+        <v>218.150173442974</v>
       </c>
       <c r="G7">
         <v>79.8</v>
@@ -1861,28 +1861,28 @@
         <v>112.68</v>
       </c>
       <c r="M7">
-        <v>9.416815820288376</v>
+        <v>11.30017898434605</v>
       </c>
       <c r="N7">
-        <v>103.2631841797116</v>
+        <v>101.379821015654</v>
       </c>
       <c r="O7">
-        <v>10.32631841797116</v>
+        <v>10.1379821015654</v>
       </c>
       <c r="P7">
-        <v>92.93686576174046</v>
+        <v>91.24183891408856</v>
       </c>
       <c r="Q7">
-        <v>203.3368657617405</v>
+        <v>201.6418389140886</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09071063397762845</v>
+        <v>0.09114279019039298</v>
       </c>
       <c r="T7">
-        <v>0.9001734768095319</v>
+        <v>0.9088354689952326</v>
       </c>
       <c r="U7">
         <v>0.0518</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>11.9658281685018</v>
+        <v>9.971523473751498</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0884714227789694</v>
+        <v>0.08854384327919176</v>
       </c>
       <c r="C8">
-        <v>3439.426025054966</v>
+        <v>3397.005869533821</v>
       </c>
       <c r="D8">
-        <v>3577.776198497939</v>
+        <v>3571.714405217291</v>
       </c>
       <c r="E8">
-        <v>12.21394939340826</v>
+        <v>48.57231163390389</v>
       </c>
       <c r="F8">
-        <v>218.1501734429739</v>
+        <v>254.5085356834696</v>
       </c>
       <c r="G8">
         <v>79.8</v>
@@ -1943,45 +1943,45 @@
         <v>112.68</v>
       </c>
       <c r="M8">
-        <v>11.30017898434605</v>
+        <v>13.61620665906562</v>
       </c>
       <c r="N8">
-        <v>101.379821015654</v>
+        <v>99.06379334093438</v>
       </c>
       <c r="O8">
-        <v>10.1379821015654</v>
+        <v>9.906379334093439</v>
       </c>
       <c r="P8">
-        <v>91.24183891408856</v>
+        <v>89.15741400684094</v>
       </c>
       <c r="Q8">
-        <v>201.6418389140886</v>
+        <v>199.5574140068409</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09114279019039298</v>
+        <v>0.09158424008515242</v>
       </c>
       <c r="T8">
-        <v>0.9088354689952326</v>
+        <v>0.9176837405827761</v>
       </c>
       <c r="U8">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V8">
         <v>0.1</v>
       </c>
       <c r="W8">
-        <v>0.04662</v>
+        <v>0.04815</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>9.9715234737515</v>
+        <v>8.275432565132085</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08854384327919176</v>
+        <v>0.08858206377941413</v>
       </c>
       <c r="C9">
-        <v>3397.005869533821</v>
+        <v>3357.45662075913</v>
       </c>
       <c r="D9">
-        <v>3571.714405217291</v>
+        <v>3568.523518683095</v>
       </c>
       <c r="E9">
-        <v>48.57231163390395</v>
+        <v>84.93067387439959</v>
       </c>
       <c r="F9">
-        <v>254.5085356834696</v>
+        <v>290.8668979239653</v>
       </c>
       <c r="G9">
         <v>79.8</v>
@@ -2025,45 +2025,45 @@
         <v>112.68</v>
       </c>
       <c r="M9">
-        <v>13.61620665906563</v>
+        <v>15.79407255727132</v>
       </c>
       <c r="N9">
-        <v>99.06379334093438</v>
+        <v>96.88592744272869</v>
       </c>
       <c r="O9">
-        <v>9.906379334093439</v>
+        <v>9.688592744272869</v>
       </c>
       <c r="P9">
-        <v>89.15741400684094</v>
+        <v>87.19733469845582</v>
       </c>
       <c r="Q9">
-        <v>199.5574140068409</v>
+        <v>197.5973346984558</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09158424008515244</v>
+        <v>0.09203528671675448</v>
       </c>
       <c r="T9">
-        <v>0.9176837405827764</v>
+        <v>0.9267243659004839</v>
       </c>
       <c r="U9">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V9">
         <v>0.1</v>
       </c>
       <c r="W9">
-        <v>0.04815</v>
+        <v>0.04887</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y9">
-        <v>8.275432565132084</v>
+        <v>7.13432204337469</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08858206377941413</v>
+        <v>0.08856988427963648</v>
       </c>
       <c r="C10">
-        <v>3357.45662075913</v>
+        <v>3322.114460272143</v>
       </c>
       <c r="D10">
-        <v>3568.523518683095</v>
+        <v>3569.539720436604</v>
       </c>
       <c r="E10">
-        <v>84.93067387439959</v>
+        <v>121.2890361148952</v>
       </c>
       <c r="F10">
-        <v>290.8668979239653</v>
+        <v>327.2252601644609</v>
       </c>
       <c r="G10">
         <v>79.8</v>
@@ -2107,28 +2107,28 @@
         <v>112.68</v>
       </c>
       <c r="M10">
-        <v>15.79407255727132</v>
+        <v>17.76833162693023</v>
       </c>
       <c r="N10">
-        <v>96.88592744272869</v>
+        <v>94.91166837306977</v>
       </c>
       <c r="O10">
-        <v>9.688592744272869</v>
+        <v>9.491166837306977</v>
       </c>
       <c r="P10">
-        <v>87.19733469845582</v>
+        <v>85.4205015357628</v>
       </c>
       <c r="Q10">
-        <v>197.5973346984558</v>
+        <v>195.8205015357628</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09203528671675448</v>
+        <v>0.09249624646113899</v>
       </c>
       <c r="T10">
-        <v>0.9267243659004839</v>
+        <v>0.9359636862801191</v>
       </c>
       <c r="U10">
         <v>0.0543</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>7.13432204337469</v>
+        <v>6.341619594110837</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08856988427963648</v>
+        <v>0.08864770477985885</v>
       </c>
       <c r="C11">
-        <v>3322.114460272143</v>
+        <v>3279.273058437457</v>
       </c>
       <c r="D11">
-        <v>3569.539720436604</v>
+        <v>3563.056680842414</v>
       </c>
       <c r="E11">
-        <v>121.2890361148952</v>
+        <v>157.6473983553909</v>
       </c>
       <c r="F11">
-        <v>327.2252601644609</v>
+        <v>363.5836224049565</v>
       </c>
       <c r="G11">
         <v>79.8</v>
@@ -2189,45 +2189,45 @@
         <v>112.68</v>
       </c>
       <c r="M11">
-        <v>17.76833162693023</v>
+        <v>20.1061743189941</v>
       </c>
       <c r="N11">
-        <v>94.91166837306977</v>
+        <v>92.57382568100591</v>
       </c>
       <c r="O11">
-        <v>9.491166837306977</v>
+        <v>9.257382568100592</v>
       </c>
       <c r="P11">
-        <v>85.4205015357628</v>
+        <v>83.31644311290532</v>
       </c>
       <c r="Q11">
-        <v>195.8205015357628</v>
+        <v>193.7164431129053</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09249624646113899</v>
+        <v>0.09296744975539872</v>
       </c>
       <c r="T11">
-        <v>0.9359636862801191</v>
+        <v>0.945408324890413</v>
       </c>
       <c r="U11">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V11">
         <v>0.1</v>
       </c>
       <c r="W11">
-        <v>0.04887</v>
+        <v>0.04977</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y11">
-        <v>6.341619594110837</v>
+        <v>5.60424863588059</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08864770477985885</v>
+        <v>0.08864452528008122</v>
       </c>
       <c r="C12">
-        <v>3279.273058437457</v>
+        <v>3243.179111261672</v>
       </c>
       <c r="D12">
-        <v>3563.056680842414</v>
+        <v>3563.321095907124</v>
       </c>
       <c r="E12">
-        <v>157.6473983553909</v>
+        <v>194.0057605958866</v>
       </c>
       <c r="F12">
-        <v>363.5836224049566</v>
+        <v>399.9419846454522</v>
       </c>
       <c r="G12">
         <v>79.8</v>
@@ -2271,28 +2271,28 @@
         <v>112.68</v>
       </c>
       <c r="M12">
-        <v>20.1061743189941</v>
+        <v>22.11679175089351</v>
       </c>
       <c r="N12">
-        <v>92.5738256810059</v>
+        <v>90.56320824910649</v>
       </c>
       <c r="O12">
-        <v>9.25738256810059</v>
+        <v>9.056320824910649</v>
       </c>
       <c r="P12">
-        <v>83.3164431129053</v>
+        <v>81.50688742419584</v>
       </c>
       <c r="Q12">
-        <v>193.7164431129053</v>
+        <v>191.9068874241958</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09296744975539872</v>
+        <v>0.09344924188773171</v>
       </c>
       <c r="T12">
-        <v>0.945408324890413</v>
+        <v>0.955065202570601</v>
       </c>
       <c r="U12">
         <v>0.0553</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>5.604248635880588</v>
+        <v>5.094771487164172</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08864452528008122</v>
+        <v>0.08864134578030358</v>
       </c>
       <c r="C13">
-        <v>3243.179111261672</v>
+        <v>3207.085203333378</v>
       </c>
       <c r="D13">
-        <v>3563.321095907124</v>
+        <v>3563.585550219325</v>
       </c>
       <c r="E13">
-        <v>194.0057605958866</v>
+        <v>230.3641228363822</v>
       </c>
       <c r="F13">
-        <v>399.9419846454522</v>
+        <v>436.3003468859479</v>
       </c>
       <c r="G13">
         <v>79.8</v>
@@ -2353,28 +2353,28 @@
         <v>112.68</v>
       </c>
       <c r="M13">
-        <v>22.11679175089351</v>
+        <v>24.12740918279292</v>
       </c>
       <c r="N13">
-        <v>90.56320824910649</v>
+        <v>88.55259081720709</v>
       </c>
       <c r="O13">
-        <v>9.056320824910649</v>
+        <v>8.855259081720709</v>
       </c>
       <c r="P13">
-        <v>81.50688742419584</v>
+        <v>79.69733173548639</v>
       </c>
       <c r="Q13">
-        <v>191.9068874241958</v>
+        <v>190.0973317354864</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09344924188773171</v>
+        <v>0.09394198384125407</v>
       </c>
       <c r="T13">
-        <v>0.955065202570601</v>
+        <v>0.9649415547435207</v>
       </c>
       <c r="U13">
         <v>0.0553</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>5.094771487164172</v>
+        <v>4.670207196567158</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08864134578030358</v>
+        <v>0.08893066628052596</v>
       </c>
       <c r="C14">
-        <v>3207.085203333378</v>
+        <v>3146.822309981101</v>
       </c>
       <c r="D14">
-        <v>3563.585550219325</v>
+        <v>3539.681019107544</v>
       </c>
       <c r="E14">
-        <v>230.3641228363822</v>
+        <v>266.7224850768779</v>
       </c>
       <c r="F14">
-        <v>436.3003468859479</v>
+        <v>472.6587091264436</v>
       </c>
       <c r="G14">
         <v>79.8</v>
@@ -2435,45 +2435,45 @@
         <v>112.68</v>
       </c>
       <c r="M14">
-        <v>24.12740918279292</v>
+        <v>27.31967338750844</v>
       </c>
       <c r="N14">
-        <v>88.55259081720709</v>
+        <v>85.36032661249156</v>
       </c>
       <c r="O14">
-        <v>8.855259081720709</v>
+        <v>8.536032661249157</v>
       </c>
       <c r="P14">
-        <v>79.69733173548639</v>
+        <v>76.82429395124241</v>
       </c>
       <c r="Q14">
-        <v>190.0973317354864</v>
+        <v>187.2242939512424</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09394198384125407</v>
+        <v>0.09444605319600684</v>
       </c>
       <c r="T14">
-        <v>0.9649415547435207</v>
+        <v>0.9750449494951281</v>
       </c>
       <c r="U14">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V14">
         <v>0.1</v>
       </c>
       <c r="W14">
-        <v>0.04977</v>
+        <v>0.05202</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y14">
-        <v>4.670207196567158</v>
+        <v>4.124500260369929</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08893066628052596</v>
+        <v>0.0893909867807483</v>
       </c>
       <c r="C15">
-        <v>3146.822309981101</v>
+        <v>3073.084942178319</v>
       </c>
       <c r="D15">
-        <v>3539.681019107544</v>
+        <v>3502.302013545258</v>
       </c>
       <c r="E15">
-        <v>266.7224850768779</v>
+        <v>303.0808473173736</v>
       </c>
       <c r="F15">
-        <v>472.6587091264436</v>
+        <v>509.0170713669393</v>
       </c>
       <c r="G15">
         <v>79.8</v>
@@ -2517,45 +2517,45 @@
         <v>112.68</v>
       </c>
       <c r="M15">
-        <v>27.31967338750844</v>
+        <v>31.20274647479338</v>
       </c>
       <c r="N15">
-        <v>85.36032661249156</v>
+        <v>81.47725352520663</v>
       </c>
       <c r="O15">
-        <v>8.536032661249157</v>
+        <v>8.147725352520665</v>
       </c>
       <c r="P15">
-        <v>76.82429395124241</v>
+        <v>73.32952817268597</v>
       </c>
       <c r="Q15">
-        <v>187.2242939512424</v>
+        <v>183.729528172686</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09444605319600684</v>
+        <v>0.09496184509389338</v>
       </c>
       <c r="T15">
-        <v>0.9750449494951281</v>
+        <v>0.9853833069153776</v>
       </c>
       <c r="U15">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V15">
         <v>0.1</v>
       </c>
       <c r="W15">
-        <v>0.05202</v>
+        <v>0.05517</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>4.124500260369929</v>
+        <v>3.611220572875746</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0893909867807483</v>
+        <v>0.08981980728097069</v>
       </c>
       <c r="C16">
-        <v>3073.084942178319</v>
+        <v>3002.6087817432</v>
       </c>
       <c r="D16">
-        <v>3502.302013545258</v>
+        <v>3468.184215350635</v>
       </c>
       <c r="E16">
-        <v>303.0808473173736</v>
+        <v>339.4392095578693</v>
       </c>
       <c r="F16">
-        <v>509.0170713669393</v>
+        <v>545.375433607435</v>
       </c>
       <c r="G16">
         <v>79.8</v>
@@ -2599,45 +2599,45 @@
         <v>112.68</v>
       </c>
       <c r="M16">
-        <v>31.20274647479338</v>
+        <v>34.95856529423659</v>
       </c>
       <c r="N16">
-        <v>81.47725352520663</v>
+        <v>77.72143470576341</v>
       </c>
       <c r="O16">
-        <v>8.147725352520665</v>
+        <v>7.772143470576342</v>
       </c>
       <c r="P16">
-        <v>73.32952817268597</v>
+        <v>69.94929123518708</v>
       </c>
       <c r="Q16">
-        <v>183.729528172686</v>
+        <v>180.3492912351871</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09496184509389338</v>
+        <v>0.09548977327173022</v>
       </c>
       <c r="T16">
-        <v>0.9853833069153776</v>
+        <v>0.9959649198043389</v>
       </c>
       <c r="U16">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V16">
         <v>0.1</v>
       </c>
       <c r="W16">
-        <v>0.05517</v>
+        <v>0.05769000000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y16">
-        <v>3.611220572875746</v>
+        <v>3.223244405243853</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08981980728097068</v>
+        <v>0.08989582778119304</v>
       </c>
       <c r="C17">
-        <v>3002.608781743201</v>
+        <v>2960.271325511716</v>
       </c>
       <c r="D17">
-        <v>3468.184215350636</v>
+        <v>3462.205121359646</v>
       </c>
       <c r="E17">
-        <v>339.4392095578692</v>
+        <v>375.7975717983649</v>
       </c>
       <c r="F17">
-        <v>545.3754336074348</v>
+        <v>581.7337958479305</v>
       </c>
       <c r="G17">
         <v>79.8</v>
@@ -2681,28 +2681,28 @@
         <v>112.68</v>
       </c>
       <c r="M17">
-        <v>34.95856529423658</v>
+        <v>37.28913631385235</v>
       </c>
       <c r="N17">
-        <v>77.72143470576343</v>
+        <v>75.39086368614765</v>
       </c>
       <c r="O17">
-        <v>7.772143470576343</v>
+        <v>7.539086368614766</v>
       </c>
       <c r="P17">
-        <v>69.94929123518709</v>
+        <v>67.85177731753289</v>
       </c>
       <c r="Q17">
-        <v>180.3492912351871</v>
+        <v>178.2517773175329</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09548977327173022</v>
+        <v>0.09603027116808696</v>
       </c>
       <c r="T17">
-        <v>0.9959649198043389</v>
+        <v>1.006798475857323</v>
       </c>
       <c r="U17">
         <v>0.0641</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>3.223244405243854</v>
+        <v>3.021791629916112</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08989582778119304</v>
+        <v>0.0911652482814154</v>
       </c>
       <c r="C18">
-        <v>2960.271325511716</v>
+        <v>2827.032767008099</v>
       </c>
       <c r="D18">
-        <v>3462.205121359646</v>
+        <v>3365.324925096525</v>
       </c>
       <c r="E18">
-        <v>375.7975717983649</v>
+        <v>412.1559340388606</v>
       </c>
       <c r="F18">
-        <v>581.7337958479305</v>
+        <v>618.0921580884262</v>
       </c>
       <c r="G18">
         <v>79.8</v>
@@ -2763,45 +2763,45 @@
         <v>112.68</v>
       </c>
       <c r="M18">
-        <v>37.28913631385235</v>
+        <v>44.44082616655785</v>
       </c>
       <c r="N18">
-        <v>75.39086368614765</v>
+        <v>68.23917383344215</v>
       </c>
       <c r="O18">
-        <v>7.539086368614766</v>
+        <v>6.823917383344216</v>
       </c>
       <c r="P18">
-        <v>67.85177731753289</v>
+        <v>61.41525645009794</v>
       </c>
       <c r="Q18">
-        <v>178.2517773175329</v>
+        <v>171.8152564500979</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09603027116808696</v>
+        <v>0.09658379311013904</v>
       </c>
       <c r="T18">
-        <v>1.006798475857323</v>
+        <v>1.017893081453752</v>
       </c>
       <c r="U18">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V18">
         <v>0.1</v>
       </c>
       <c r="W18">
-        <v>0.05769000000000001</v>
+        <v>0.06471</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>3.021791629916112</v>
+        <v>2.535506418753142</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0911652482814154</v>
+        <v>0.09194326878163776</v>
       </c>
       <c r="C19">
-        <v>2827.032767008099</v>
+        <v>2733.931745420584</v>
       </c>
       <c r="D19">
-        <v>3365.324925096525</v>
+        <v>3308.582265749506</v>
       </c>
       <c r="E19">
-        <v>412.1559340388606</v>
+        <v>448.5142962793562</v>
       </c>
       <c r="F19">
-        <v>618.0921580884262</v>
+        <v>654.4505203289219</v>
       </c>
       <c r="G19">
         <v>79.8</v>
@@ -2845,45 +2845,45 @@
         <v>112.68</v>
       </c>
       <c r="M19">
-        <v>44.44082616655785</v>
+        <v>49.60734944093229</v>
       </c>
       <c r="N19">
-        <v>68.23917383344215</v>
+        <v>63.07265055906772</v>
       </c>
       <c r="O19">
-        <v>6.823917383344216</v>
+        <v>6.307265055906772</v>
       </c>
       <c r="P19">
-        <v>61.41525645009794</v>
+        <v>56.76538550316094</v>
       </c>
       <c r="Q19">
-        <v>171.8152564500979</v>
+        <v>167.165385503161</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09658379311013904</v>
+        <v>0.09715081558736313</v>
       </c>
       <c r="T19">
-        <v>1.017893081453752</v>
+        <v>1.02925828718668</v>
       </c>
       <c r="U19">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V19">
         <v>0.1</v>
       </c>
       <c r="W19">
-        <v>0.06471</v>
+        <v>0.06822</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y19">
-        <v>2.535506418753142</v>
+        <v>2.271437625067403</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09194326878163778</v>
+        <v>0.09212458928186014</v>
       </c>
       <c r="C20">
-        <v>2733.931745420583</v>
+        <v>2684.62315953531</v>
       </c>
       <c r="D20">
-        <v>3308.582265749505</v>
+        <v>3295.632042104728</v>
       </c>
       <c r="E20">
-        <v>448.5142962793561</v>
+        <v>484.8726585198518</v>
       </c>
       <c r="F20">
-        <v>654.4505203289218</v>
+        <v>690.8088825694175</v>
       </c>
       <c r="G20">
         <v>79.8</v>
@@ -2927,28 +2927,28 @@
         <v>112.68</v>
       </c>
       <c r="M20">
-        <v>49.60734944093227</v>
+        <v>52.36331329876185</v>
       </c>
       <c r="N20">
-        <v>63.07265055906773</v>
+        <v>60.31668670123815</v>
       </c>
       <c r="O20">
-        <v>6.307265055906774</v>
+        <v>6.031668670123816</v>
       </c>
       <c r="P20">
-        <v>56.76538550316096</v>
+        <v>54.28501803111434</v>
       </c>
       <c r="Q20">
-        <v>167.165385503161</v>
+        <v>164.6850180311143</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09715081558736313</v>
+        <v>0.09773183861958042</v>
       </c>
       <c r="T20">
-        <v>1.02925828718668</v>
+        <v>1.040904115283384</v>
       </c>
       <c r="U20">
         <v>0.07580000000000001</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>2.271437625067404</v>
+        <v>2.151888276379645</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09212458928186014</v>
+        <v>0.09230590978208252</v>
       </c>
       <c r="C21">
-        <v>2684.62315953531</v>
+        <v>2635.415556129049</v>
       </c>
       <c r="D21">
-        <v>3295.632042104728</v>
+        <v>3282.782800938962</v>
       </c>
       <c r="E21">
-        <v>484.8726585198518</v>
+        <v>521.2310207603475</v>
       </c>
       <c r="F21">
-        <v>690.8088825694175</v>
+        <v>727.1672448099132</v>
       </c>
       <c r="G21">
         <v>79.8</v>
@@ -3009,28 +3009,28 @@
         <v>112.68</v>
       </c>
       <c r="M21">
-        <v>52.36331329876185</v>
+        <v>55.11927715659142</v>
       </c>
       <c r="N21">
-        <v>60.31668670123815</v>
+        <v>57.56072284340858</v>
       </c>
       <c r="O21">
-        <v>6.031668670123816</v>
+        <v>5.756072284340859</v>
       </c>
       <c r="P21">
-        <v>54.28501803111434</v>
+        <v>51.80465055906772</v>
       </c>
       <c r="Q21">
-        <v>164.6850180311143</v>
+        <v>162.2046505590677</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09773183861958042</v>
+        <v>0.09832738722760313</v>
       </c>
       <c r="T21">
-        <v>1.040904115283384</v>
+        <v>1.052841089082506</v>
       </c>
       <c r="U21">
         <v>0.07580000000000001</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>2.151888276379645</v>
+        <v>2.044293862560663</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09230590978208252</v>
+        <v>0.09517103028230486</v>
       </c>
       <c r="C22">
-        <v>2635.415556129049</v>
+        <v>2408.549354636136</v>
       </c>
       <c r="D22">
-        <v>3282.782800938962</v>
+        <v>3092.274961686545</v>
       </c>
       <c r="E22">
-        <v>521.2310207603475</v>
+        <v>557.5893830008432</v>
       </c>
       <c r="F22">
-        <v>727.1672448099132</v>
+        <v>763.5256070504089</v>
       </c>
       <c r="G22">
         <v>79.8</v>
@@ -3091,45 +3091,45 @@
         <v>112.68</v>
       </c>
       <c r="M22">
-        <v>55.11927715659142</v>
+        <v>68.7173046345368</v>
       </c>
       <c r="N22">
-        <v>57.56072284340858</v>
+        <v>43.9626953654632</v>
       </c>
       <c r="O22">
-        <v>5.756072284340859</v>
+        <v>4.39626953654632</v>
       </c>
       <c r="P22">
-        <v>51.80465055906772</v>
+        <v>39.56642582891688</v>
       </c>
       <c r="Q22">
-        <v>162.2046505590677</v>
+        <v>149.9664258289169</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09832738722760313</v>
+        <v>0.09893801301557578</v>
       </c>
       <c r="T22">
-        <v>1.052841089082506</v>
+        <v>1.065080264749959</v>
       </c>
       <c r="U22">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V22">
         <v>0.1</v>
       </c>
       <c r="W22">
-        <v>0.06822</v>
+        <v>0.081</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>2.044293862560663</v>
+        <v>1.639761637905802</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09517103028230486</v>
+        <v>0.09548015078252722</v>
       </c>
       <c r="C23">
-        <v>2408.549354636136</v>
+        <v>2352.950197673298</v>
       </c>
       <c r="D23">
-        <v>3092.274961686545</v>
+        <v>3073.034166964203</v>
       </c>
       <c r="E23">
-        <v>557.5893830008431</v>
+        <v>593.9477452413388</v>
       </c>
       <c r="F23">
-        <v>763.5256070504088</v>
+        <v>799.8839692909045</v>
       </c>
       <c r="G23">
         <v>79.8</v>
@@ -3173,28 +3173,28 @@
         <v>112.68</v>
       </c>
       <c r="M23">
-        <v>68.71730463453679</v>
+        <v>71.9895572361814</v>
       </c>
       <c r="N23">
-        <v>43.96269536546322</v>
+        <v>40.69044276381861</v>
       </c>
       <c r="O23">
-        <v>4.396269536546322</v>
+        <v>4.069044276381861</v>
       </c>
       <c r="P23">
-        <v>39.5664258289169</v>
+        <v>36.62139848743675</v>
       </c>
       <c r="Q23">
-        <v>149.9664258289169</v>
+        <v>147.0213984874368</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09893801301557578</v>
+        <v>0.0995642958750349</v>
       </c>
       <c r="T23">
-        <v>1.065080264749959</v>
+        <v>1.077633265434527</v>
       </c>
       <c r="U23">
         <v>0.09</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>1.639761637905802</v>
+        <v>1.565227018000993</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09548015078252722</v>
+        <v>0.1079051051858813</v>
       </c>
       <c r="C24">
-        <v>2352.950197673298</v>
+        <v>1701.790374422484</v>
       </c>
       <c r="D24">
-        <v>3073.034166964203</v>
+        <v>2458.232705953884</v>
       </c>
       <c r="E24">
-        <v>593.9477452413388</v>
+        <v>630.3061074818345</v>
       </c>
       <c r="F24">
-        <v>799.8839692909045</v>
+        <v>836.2423315314002</v>
       </c>
       <c r="G24">
         <v>79.8</v>
@@ -3255,45 +3255,45 @@
         <v>112.68</v>
       </c>
       <c r="M24">
-        <v>71.9895572361814</v>
+        <v>122.7603742688096</v>
       </c>
       <c r="N24">
-        <v>40.69044276381861</v>
+        <v>-10.08037426880955</v>
       </c>
       <c r="O24">
-        <v>4.069044276381861</v>
+        <v>-1.008037426880955</v>
       </c>
       <c r="P24">
-        <v>36.62139848743675</v>
+        <v>-9.072336841928594</v>
       </c>
       <c r="Q24">
-        <v>147.0213984874368</v>
+        <v>101.3276631580714</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.0995642958750349</v>
+        <v>0.1003120190669133</v>
       </c>
       <c r="T24">
-        <v>1.077633265434527</v>
+        <v>1.092620374849628</v>
       </c>
       <c r="U24">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V24">
-        <v>0.1</v>
+        <v>0.09178857646137796</v>
       </c>
       <c r="W24">
-        <v>0.081</v>
+        <v>0.1333254369754697</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y24">
-        <v>1.565227018000993</v>
+        <v>0.9178857646137796</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1079051051858813</v>
+        <v>0.1089151051858813</v>
       </c>
       <c r="C25">
-        <v>1701.790374422484</v>
+        <v>1626.094122691014</v>
       </c>
       <c r="D25">
-        <v>2458.232705953884</v>
+        <v>2418.89481646291</v>
       </c>
       <c r="E25">
-        <v>630.3061074818345</v>
+        <v>666.6644697223302</v>
       </c>
       <c r="F25">
-        <v>836.2423315314002</v>
+        <v>872.6006937718959</v>
       </c>
       <c r="G25">
         <v>79.8</v>
@@ -3337,37 +3337,37 @@
         <v>112.68</v>
       </c>
       <c r="M25">
-        <v>122.7603742688096</v>
+        <v>128.0977818457143</v>
       </c>
       <c r="N25">
-        <v>-10.08037426880955</v>
+        <v>-15.41778184571433</v>
       </c>
       <c r="O25">
-        <v>-1.008037426880955</v>
+        <v>-1.541778184571433</v>
       </c>
       <c r="P25">
-        <v>-9.072336841928594</v>
+        <v>-13.8760036611429</v>
       </c>
       <c r="Q25">
-        <v>101.3276631580714</v>
+        <v>96.5239963388571</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1003120190669133</v>
+        <v>0.1010292824756885</v>
       </c>
       <c r="T25">
-        <v>1.092620374849628</v>
+        <v>1.106996958729228</v>
       </c>
       <c r="U25">
         <v>0.1468</v>
       </c>
       <c r="V25">
-        <v>0.09178857646137796</v>
+        <v>0.08796405244215387</v>
       </c>
       <c r="W25">
-        <v>0.1333254369754697</v>
+        <v>0.1338868771014918</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.9178857646137796</v>
+        <v>0.8796405244215386</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1089151051858813</v>
+        <v>0.1099251051858813</v>
       </c>
       <c r="C26">
-        <v>1626.094122691014</v>
+        <v>1551.637050786874</v>
       </c>
       <c r="D26">
-        <v>2418.89481646291</v>
+        <v>2380.796106799265</v>
       </c>
       <c r="E26">
-        <v>666.6644697223301</v>
+        <v>703.0228319628258</v>
       </c>
       <c r="F26">
-        <v>872.6006937718957</v>
+        <v>908.9590560123914</v>
       </c>
       <c r="G26">
         <v>79.8</v>
@@ -3419,37 +3419,37 @@
         <v>112.68</v>
       </c>
       <c r="M26">
-        <v>128.0977818457143</v>
+        <v>133.4351894226191</v>
       </c>
       <c r="N26">
-        <v>-15.4177818457143</v>
+        <v>-20.75518942261908</v>
       </c>
       <c r="O26">
-        <v>-1.54177818457143</v>
+        <v>-2.075518942261908</v>
       </c>
       <c r="P26">
-        <v>-13.87600366114287</v>
+        <v>-18.67967048035717</v>
       </c>
       <c r="Q26">
-        <v>96.52399633885713</v>
+        <v>91.72032951964283</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1010292824756885</v>
+        <v>0.1017656729086976</v>
       </c>
       <c r="T26">
-        <v>1.106996958729228</v>
+        <v>1.121756918178951</v>
       </c>
       <c r="U26">
         <v>0.1468</v>
       </c>
       <c r="V26">
-        <v>0.08796405244215388</v>
+        <v>0.08444549034446772</v>
       </c>
       <c r="W26">
-        <v>0.1338868771014918</v>
+        <v>0.1344034020174321</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.8796405244215388</v>
+        <v>0.8444549034446771</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1099251051858813</v>
+        <v>0.1109351051858813</v>
       </c>
       <c r="C27">
-        <v>1551.637050786874</v>
+        <v>1478.361513683376</v>
       </c>
       <c r="D27">
-        <v>2380.796106799265</v>
+        <v>2343.878931936263</v>
       </c>
       <c r="E27">
-        <v>703.0228319628258</v>
+        <v>739.3811942033215</v>
       </c>
       <c r="F27">
-        <v>908.9590560123914</v>
+        <v>945.3174182528871</v>
       </c>
       <c r="G27">
         <v>79.8</v>
@@ -3501,37 +3501,37 @@
         <v>112.68</v>
       </c>
       <c r="M27">
-        <v>133.4351894226191</v>
+        <v>138.7725969995238</v>
       </c>
       <c r="N27">
-        <v>-20.75518942261908</v>
+        <v>-26.09259699952383</v>
       </c>
       <c r="O27">
-        <v>-2.075518942261908</v>
+        <v>-2.609259699952384</v>
       </c>
       <c r="P27">
-        <v>-18.67967048035717</v>
+        <v>-23.48333729957145</v>
       </c>
       <c r="Q27">
-        <v>91.72032951964283</v>
+        <v>86.91666270042856</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1017656729086976</v>
+        <v>0.1025219657858422</v>
       </c>
       <c r="T27">
-        <v>1.121756918178951</v>
+        <v>1.13691579545164</v>
       </c>
       <c r="U27">
         <v>0.1468</v>
       </c>
       <c r="V27">
-        <v>0.08444549034446772</v>
+        <v>0.08119758686968051</v>
       </c>
       <c r="W27">
-        <v>0.1344034020174321</v>
+        <v>0.1348801942475309</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.8444549034446771</v>
+        <v>0.811975868696805</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1109351051858813</v>
+        <v>0.1267685475922062</v>
       </c>
       <c r="C28">
-        <v>1478.361513683376</v>
+        <v>983.6563837186742</v>
       </c>
       <c r="D28">
-        <v>2343.878931936263</v>
+        <v>1885.532164212057</v>
       </c>
       <c r="E28">
-        <v>739.3811942033215</v>
+        <v>775.7395564438172</v>
       </c>
       <c r="F28">
-        <v>945.3174182528871</v>
+        <v>981.6757804933828</v>
       </c>
       <c r="G28">
         <v>79.8</v>
@@ -3583,45 +3583,45 @@
         <v>112.68</v>
       </c>
       <c r="M28">
-        <v>138.7725969995238</v>
+        <v>197.1204967230713</v>
       </c>
       <c r="N28">
-        <v>-26.09259699952383</v>
+        <v>-84.44049672307128</v>
       </c>
       <c r="O28">
-        <v>-2.609259699952384</v>
+        <v>-8.444049672307129</v>
       </c>
       <c r="P28">
-        <v>-23.48333729957145</v>
+        <v>-75.99644705076415</v>
       </c>
       <c r="Q28">
-        <v>86.91666270042856</v>
+        <v>34.40355294923586</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1025219657858422</v>
+        <v>0.1036324617641756</v>
       </c>
       <c r="T28">
-        <v>1.13691579545164</v>
+        <v>1.159174199247438</v>
       </c>
       <c r="U28">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V28">
-        <v>0.08119758686968051</v>
+        <v>0.05716300530548114</v>
       </c>
       <c r="W28">
-        <v>0.1348801942475309</v>
+        <v>0.1893216685346594</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y28">
-        <v>0.811975868696805</v>
+        <v>0.5716300530548113</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1267685475922062</v>
+        <v>0.1283185475922062</v>
       </c>
       <c r="C29">
-        <v>983.6563837186742</v>
+        <v>911.8808341935501</v>
       </c>
       <c r="D29">
-        <v>1885.532164212057</v>
+        <v>1850.114976927429</v>
       </c>
       <c r="E29">
-        <v>775.7395564438172</v>
+        <v>812.0979186843128</v>
       </c>
       <c r="F29">
-        <v>981.6757804933828</v>
+        <v>1018.034142733879</v>
       </c>
       <c r="G29">
         <v>79.8</v>
@@ -3665,37 +3665,37 @@
         <v>112.68</v>
       </c>
       <c r="M29">
-        <v>197.1204967230713</v>
+        <v>204.4212558609628</v>
       </c>
       <c r="N29">
-        <v>-84.44049672307128</v>
+        <v>-91.74125586096281</v>
       </c>
       <c r="O29">
-        <v>-8.444049672307129</v>
+        <v>-9.174125586096281</v>
       </c>
       <c r="P29">
-        <v>-75.99644705076415</v>
+        <v>-82.56713027486653</v>
       </c>
       <c r="Q29">
-        <v>34.40355294923586</v>
+        <v>27.83286972513348</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1036324617641756</v>
+        <v>0.1044356903997891</v>
       </c>
       <c r="T29">
-        <v>1.159174199247438</v>
+        <v>1.175273840903653</v>
       </c>
       <c r="U29">
         <v>0.2008</v>
       </c>
       <c r="V29">
-        <v>0.05716300530548114</v>
+        <v>0.05512146940171395</v>
       </c>
       <c r="W29">
-        <v>0.1893216685346594</v>
+        <v>0.1897316089441358</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.5716300530548113</v>
+        <v>0.5512146940171395</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1283185475922062</v>
+        <v>0.1298685475922062</v>
       </c>
       <c r="C30">
-        <v>911.8808341935501</v>
+        <v>841.4112817830062</v>
       </c>
       <c r="D30">
-        <v>1850.114976927429</v>
+        <v>1816.00378675738</v>
       </c>
       <c r="E30">
-        <v>812.0979186843128</v>
+        <v>848.4562809248084</v>
       </c>
       <c r="F30">
-        <v>1018.034142733879</v>
+        <v>1054.392504974374</v>
       </c>
       <c r="G30">
         <v>79.8</v>
@@ -3747,37 +3747,37 @@
         <v>112.68</v>
       </c>
       <c r="M30">
-        <v>204.4212558609628</v>
+        <v>211.7220149988543</v>
       </c>
       <c r="N30">
-        <v>-91.74125586096281</v>
+        <v>-99.04201499885431</v>
       </c>
       <c r="O30">
-        <v>-9.174125586096281</v>
+        <v>-9.904201499885431</v>
       </c>
       <c r="P30">
-        <v>-82.56713027486653</v>
+        <v>-89.13781349896888</v>
       </c>
       <c r="Q30">
-        <v>27.83286972513348</v>
+        <v>21.26218650103112</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1044356903997891</v>
+        <v>0.1052615451941523</v>
       </c>
       <c r="T30">
-        <v>1.175273840903653</v>
+        <v>1.191826993592436</v>
       </c>
       <c r="U30">
         <v>0.2008</v>
       </c>
       <c r="V30">
-        <v>0.05512146940171395</v>
+        <v>0.05322072907751693</v>
       </c>
       <c r="W30">
-        <v>0.1897316089441358</v>
+        <v>0.1901132776012346</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.5512146940171395</v>
+        <v>0.5322072907751693</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1298685475922062</v>
+        <v>0.1314185475922062</v>
       </c>
       <c r="C31">
-        <v>841.4112817830066</v>
+        <v>772.1767969191671</v>
       </c>
       <c r="D31">
-        <v>1816.003786757381</v>
+        <v>1783.127664134037</v>
       </c>
       <c r="E31">
-        <v>848.4562809248084</v>
+        <v>884.814643165304</v>
       </c>
       <c r="F31">
-        <v>1054.392504974374</v>
+        <v>1090.75086721487</v>
       </c>
       <c r="G31">
         <v>79.8</v>
@@ -3829,37 +3829,37 @@
         <v>112.68</v>
       </c>
       <c r="M31">
-        <v>211.7220149988543</v>
+        <v>219.0227741367459</v>
       </c>
       <c r="N31">
-        <v>-99.04201499885431</v>
+        <v>-106.3427741367458</v>
       </c>
       <c r="O31">
-        <v>-9.904201499885431</v>
+        <v>-10.63427741367459</v>
       </c>
       <c r="P31">
-        <v>-89.13781349896888</v>
+        <v>-95.70849672307126</v>
       </c>
       <c r="Q31">
-        <v>21.26218650103112</v>
+        <v>14.69150327692874</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1052615451941523</v>
+        <v>0.1061109958397831</v>
       </c>
       <c r="T31">
-        <v>1.191826993592436</v>
+        <v>1.2088530935009</v>
       </c>
       <c r="U31">
         <v>0.2008</v>
       </c>
       <c r="V31">
-        <v>0.05322072907751693</v>
+        <v>0.05144670477493303</v>
       </c>
       <c r="W31">
-        <v>0.1901132776012346</v>
+        <v>0.1904695016811934</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.5322072907751693</v>
+        <v>0.5144670477493303</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1314185475922062</v>
+        <v>0.1439167795436165</v>
       </c>
       <c r="C32">
-        <v>772.1767969191671</v>
+        <v>508.6815142764206</v>
       </c>
       <c r="D32">
-        <v>1783.127664134037</v>
+        <v>1555.990743731786</v>
       </c>
       <c r="E32">
-        <v>884.814643165304</v>
+        <v>921.1730054057998</v>
       </c>
       <c r="F32">
-        <v>1090.75086721487</v>
+        <v>1127.109229455365</v>
       </c>
       <c r="G32">
         <v>79.8</v>
@@ -3911,45 +3911,45 @@
         <v>112.68</v>
       </c>
       <c r="M32">
-        <v>219.0227741367459</v>
+        <v>265.7723563055752</v>
       </c>
       <c r="N32">
-        <v>-106.3427741367458</v>
+        <v>-153.0923563055752</v>
       </c>
       <c r="O32">
-        <v>-10.63427741367459</v>
+        <v>-15.30923563055752</v>
       </c>
       <c r="P32">
-        <v>-95.70849672307126</v>
+        <v>-137.7831206750177</v>
       </c>
       <c r="Q32">
-        <v>14.69150327692874</v>
+        <v>-27.38312067501769</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1061109958397831</v>
+        <v>0.1071274333902296</v>
       </c>
       <c r="T32">
-        <v>1.2088530935009</v>
+        <v>1.229226222150142</v>
       </c>
       <c r="U32">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.05144670477493303</v>
+        <v>0.0423971859099013</v>
       </c>
       <c r="W32">
-        <v>0.1904695016811934</v>
+        <v>0.2258027435624453</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y32">
-        <v>0.5144670477493303</v>
+        <v>0.423971859099013</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1439167795436165</v>
+        <v>0.1458167795436165</v>
       </c>
       <c r="C33">
-        <v>508.6815142764206</v>
+        <v>442.7642877475464</v>
       </c>
       <c r="D33">
-        <v>1555.990743731786</v>
+        <v>1526.431879443408</v>
       </c>
       <c r="E33">
-        <v>921.1730054057998</v>
+        <v>957.5313676462954</v>
       </c>
       <c r="F33">
-        <v>1127.109229455365</v>
+        <v>1163.467591695861</v>
       </c>
       <c r="G33">
         <v>79.8</v>
@@ -3993,37 +3993,37 @@
         <v>112.68</v>
       </c>
       <c r="M33">
-        <v>265.7723563055752</v>
+        <v>274.3456581218841</v>
       </c>
       <c r="N33">
-        <v>-153.0923563055752</v>
+        <v>-161.6656581218841</v>
       </c>
       <c r="O33">
-        <v>-15.30923563055752</v>
+        <v>-16.16656581218841</v>
       </c>
       <c r="P33">
-        <v>-137.7831206750177</v>
+        <v>-145.4990923096957</v>
       </c>
       <c r="Q33">
-        <v>-27.38312067501769</v>
+        <v>-35.09909230969566</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1071274333902296</v>
+        <v>0.1080293074106742</v>
       </c>
       <c r="T33">
-        <v>1.229226222150142</v>
+        <v>1.247303078358232</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.0423971859099013</v>
+        <v>0.04107227385021689</v>
       </c>
       <c r="W33">
-        <v>0.2258027435624453</v>
+        <v>0.2261151578261189</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.423971859099013</v>
+        <v>0.4107227385021689</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1458167795436165</v>
+        <v>0.1477167795436165</v>
       </c>
       <c r="C34">
-        <v>442.7642877475464</v>
+        <v>377.9491730082996</v>
       </c>
       <c r="D34">
-        <v>1526.431879443408</v>
+        <v>1497.975126944656</v>
       </c>
       <c r="E34">
-        <v>957.5313676462954</v>
+        <v>993.889729886791</v>
       </c>
       <c r="F34">
-        <v>1163.467591695861</v>
+        <v>1199.825953936357</v>
       </c>
       <c r="G34">
         <v>79.8</v>
@@ -4075,37 +4075,37 @@
         <v>112.68</v>
       </c>
       <c r="M34">
-        <v>274.3456581218841</v>
+        <v>282.9189599381929</v>
       </c>
       <c r="N34">
-        <v>-161.6656581218841</v>
+        <v>-170.2389599381929</v>
       </c>
       <c r="O34">
-        <v>-16.16656581218841</v>
+        <v>-17.02389599381929</v>
       </c>
       <c r="P34">
-        <v>-145.4990923096957</v>
+        <v>-153.2150639443736</v>
       </c>
       <c r="Q34">
-        <v>-35.09909230969566</v>
+        <v>-42.81506394437363</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1080293074106742</v>
+        <v>0.1089581030436693</v>
       </c>
       <c r="T34">
-        <v>1.247303078358232</v>
+        <v>1.265919542214325</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.04107227385021689</v>
+        <v>0.03982765949111941</v>
       </c>
       <c r="W34">
-        <v>0.2261151578261189</v>
+        <v>0.2264086378919941</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.4107227385021689</v>
+        <v>0.398276594911194</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1477167795436165</v>
+        <v>0.1496167795436165</v>
       </c>
       <c r="C35">
-        <v>377.9491730082996</v>
+        <v>314.1756592508077</v>
       </c>
       <c r="D35">
-        <v>1497.975126944656</v>
+        <v>1470.55997542766</v>
       </c>
       <c r="E35">
-        <v>993.889729886791</v>
+        <v>1030.248092127287</v>
       </c>
       <c r="F35">
-        <v>1199.825953936357</v>
+        <v>1236.184316176852</v>
       </c>
       <c r="G35">
         <v>79.8</v>
@@ -4157,37 +4157,37 @@
         <v>112.68</v>
       </c>
       <c r="M35">
-        <v>282.9189599381929</v>
+        <v>291.4922617545018</v>
       </c>
       <c r="N35">
-        <v>-170.2389599381929</v>
+        <v>-178.8122617545018</v>
       </c>
       <c r="O35">
-        <v>-17.02389599381929</v>
+        <v>-17.88122617545018</v>
       </c>
       <c r="P35">
-        <v>-153.2150639443736</v>
+        <v>-160.9310355790516</v>
       </c>
       <c r="Q35">
-        <v>-42.81506394437363</v>
+        <v>-50.53103557905163</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1089581030436693</v>
+        <v>0.1099150439988764</v>
       </c>
       <c r="T35">
-        <v>1.265919542214325</v>
+        <v>1.285100141338784</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.03982765949111941</v>
+        <v>0.0386562577413806</v>
       </c>
       <c r="W35">
-        <v>0.2264086378919941</v>
+        <v>0.2266848544245825</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.398276594911194</v>
+        <v>0.386562577413806</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1496167795436165</v>
+        <v>0.1515167795436165</v>
       </c>
       <c r="C36">
-        <v>314.1756592508077</v>
+        <v>251.3875858010356</v>
       </c>
       <c r="D36">
-        <v>1470.55997542766</v>
+        <v>1444.130264218384</v>
       </c>
       <c r="E36">
-        <v>1030.248092127287</v>
+        <v>1066.606454367782</v>
       </c>
       <c r="F36">
-        <v>1236.184316176852</v>
+        <v>1272.542678417348</v>
       </c>
       <c r="G36">
         <v>79.8</v>
@@ -4239,37 +4239,37 @@
         <v>112.68</v>
       </c>
       <c r="M36">
-        <v>291.4922617545018</v>
+        <v>300.0655635708107</v>
       </c>
       <c r="N36">
-        <v>-178.8122617545018</v>
+        <v>-187.3855635708107</v>
       </c>
       <c r="O36">
-        <v>-17.88122617545018</v>
+        <v>-18.73855635708107</v>
       </c>
       <c r="P36">
-        <v>-160.9310355790516</v>
+        <v>-168.6470072137296</v>
       </c>
       <c r="Q36">
-        <v>-50.53103557905163</v>
+        <v>-58.2470072137296</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1099150439988764</v>
+        <v>0.1109014292911669</v>
       </c>
       <c r="T36">
-        <v>1.285100141338784</v>
+        <v>1.304870912743996</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.0386562577413806</v>
+        <v>0.03755179323448402</v>
       </c>
       <c r="W36">
-        <v>0.2266848544245825</v>
+        <v>0.2269452871553087</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.386562577413806</v>
+        <v>0.3755179323448401</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1515167795436165</v>
+        <v>0.1534167795436165</v>
       </c>
       <c r="C37">
-        <v>251.3875858010356</v>
+        <v>189.5327581055139</v>
       </c>
       <c r="D37">
-        <v>1444.130264218384</v>
+        <v>1418.633798763358</v>
       </c>
       <c r="E37">
-        <v>1066.606454367782</v>
+        <v>1102.964816608278</v>
       </c>
       <c r="F37">
-        <v>1272.542678417348</v>
+        <v>1308.901040657844</v>
       </c>
       <c r="G37">
         <v>79.8</v>
@@ -4321,37 +4321,37 @@
         <v>112.68</v>
       </c>
       <c r="M37">
-        <v>300.0655635708107</v>
+        <v>308.6388653871196</v>
       </c>
       <c r="N37">
-        <v>-187.3855635708107</v>
+        <v>-195.9588653871196</v>
       </c>
       <c r="O37">
-        <v>-18.73855635708107</v>
+        <v>-19.59588653871196</v>
       </c>
       <c r="P37">
-        <v>-168.6470072137296</v>
+        <v>-176.3629788484076</v>
       </c>
       <c r="Q37">
-        <v>-58.2470072137296</v>
+        <v>-65.96297884840763</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1109014292911669</v>
+        <v>0.1119186391238413</v>
       </c>
       <c r="T37">
-        <v>1.304870912743996</v>
+        <v>1.325259520755621</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.03755179323448402</v>
+        <v>0.03650868786685945</v>
       </c>
       <c r="W37">
-        <v>0.2269452871553087</v>
+        <v>0.2271912514009946</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.3755179323448401</v>
+        <v>0.3650868786685945</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1534167795436165</v>
+        <v>0.1553167795436165</v>
       </c>
       <c r="C38">
-        <v>189.5327581055142</v>
+        <v>128.5626036914098</v>
       </c>
       <c r="D38">
-        <v>1418.633798763358</v>
+        <v>1394.022006589749</v>
       </c>
       <c r="E38">
-        <v>1102.964816608278</v>
+        <v>1139.323178848774</v>
       </c>
       <c r="F38">
-        <v>1308.901040657844</v>
+        <v>1345.259402898339</v>
       </c>
       <c r="G38">
         <v>79.8</v>
@@ -4403,37 +4403,37 @@
         <v>112.68</v>
       </c>
       <c r="M38">
-        <v>308.6388653871196</v>
+        <v>317.2121672034285</v>
       </c>
       <c r="N38">
-        <v>-195.9588653871195</v>
+        <v>-204.5321672034285</v>
       </c>
       <c r="O38">
-        <v>-19.59588653871196</v>
+        <v>-20.45321672034285</v>
       </c>
       <c r="P38">
-        <v>-176.3629788484076</v>
+        <v>-184.0789504830856</v>
       </c>
       <c r="Q38">
-        <v>-65.96297884840757</v>
+        <v>-73.6789504830856</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1119186391238413</v>
+        <v>0.1129681413321563</v>
       </c>
       <c r="T38">
-        <v>1.325259520755621</v>
+        <v>1.346295386164441</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.03650868786685946</v>
+        <v>0.03552196657316055</v>
       </c>
       <c r="W38">
-        <v>0.2271912514009946</v>
+        <v>0.2274239202820487</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.3650868786685946</v>
+        <v>0.3552196657316055</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1553167795436165</v>
+        <v>0.1572167795436165</v>
       </c>
       <c r="C39">
-        <v>128.5626036914098</v>
+        <v>68.43186332824848</v>
       </c>
       <c r="D39">
-        <v>1394.022006589749</v>
+        <v>1370.249628467084</v>
       </c>
       <c r="E39">
-        <v>1139.323178848774</v>
+        <v>1175.681541089269</v>
       </c>
       <c r="F39">
-        <v>1345.259402898339</v>
+        <v>1381.617765138835</v>
       </c>
       <c r="G39">
         <v>79.8</v>
@@ -4485,37 +4485,37 @@
         <v>112.68</v>
       </c>
       <c r="M39">
-        <v>317.2121672034285</v>
+        <v>325.7854690197373</v>
       </c>
       <c r="N39">
-        <v>-204.5321672034285</v>
+        <v>-213.1054690197373</v>
       </c>
       <c r="O39">
-        <v>-20.45321672034285</v>
+        <v>-21.31054690197373</v>
       </c>
       <c r="P39">
-        <v>-184.0789504830856</v>
+        <v>-191.7949221177636</v>
       </c>
       <c r="Q39">
-        <v>-73.6789504830856</v>
+        <v>-81.39492211776357</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1129681413321563</v>
+        <v>0.1140514984504169</v>
       </c>
       <c r="T39">
-        <v>1.346295386164441</v>
+        <v>1.36800982787677</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.03552196657316055</v>
+        <v>0.03458717797913001</v>
       </c>
       <c r="W39">
-        <v>0.2274239202820487</v>
+        <v>0.2276443434325212</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.3552196657316055</v>
+        <v>0.3458717797913001</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1572167795436165</v>
+        <v>0.1591167795436165</v>
       </c>
       <c r="C40">
-        <v>68.43186332824848</v>
+        <v>9.098313259675479</v>
       </c>
       <c r="D40">
-        <v>1370.249628467084</v>
+        <v>1347.274440639006</v>
       </c>
       <c r="E40">
-        <v>1175.681541089269</v>
+        <v>1212.039903329765</v>
       </c>
       <c r="F40">
-        <v>1381.617765138835</v>
+        <v>1417.976127379331</v>
       </c>
       <c r="G40">
         <v>79.8</v>
@@ -4567,37 +4567,37 @@
         <v>112.68</v>
       </c>
       <c r="M40">
-        <v>325.7854690197373</v>
+        <v>334.3587708360462</v>
       </c>
       <c r="N40">
-        <v>-213.1054690197373</v>
+        <v>-221.6787708360462</v>
       </c>
       <c r="O40">
-        <v>-21.31054690197373</v>
+        <v>-22.16787708360462</v>
       </c>
       <c r="P40">
-        <v>-191.7949221177636</v>
+        <v>-199.5108937524415</v>
       </c>
       <c r="Q40">
-        <v>-81.39492211776357</v>
+        <v>-89.11089375244154</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1140514984504169</v>
+        <v>0.1151703754741942</v>
       </c>
       <c r="T40">
-        <v>1.36800982787677</v>
+        <v>1.390436218497701</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.03458717797913001</v>
+        <v>0.03370032726171642</v>
       </c>
       <c r="W40">
-        <v>0.2276443434325212</v>
+        <v>0.2278534628316873</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.3458717797913001</v>
+        <v>0.3370032726171642</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1591167795436165</v>
+        <v>0.1610167795436165</v>
       </c>
       <c r="C41">
-        <v>9.098313259675479</v>
+        <v>-49.47748508130644</v>
       </c>
       <c r="D41">
-        <v>1347.274440639006</v>
+        <v>1325.05700453852</v>
       </c>
       <c r="E41">
-        <v>1212.039903329765</v>
+        <v>1248.398265570261</v>
       </c>
       <c r="F41">
-        <v>1417.976127379331</v>
+        <v>1454.334489619826</v>
       </c>
       <c r="G41">
         <v>79.8</v>
@@ -4649,37 +4649,37 @@
         <v>112.68</v>
       </c>
       <c r="M41">
-        <v>334.3587708360462</v>
+        <v>342.9320726523551</v>
       </c>
       <c r="N41">
-        <v>-221.6787708360462</v>
+        <v>-230.2520726523551</v>
       </c>
       <c r="O41">
-        <v>-22.16787708360462</v>
+        <v>-23.02520726523551</v>
       </c>
       <c r="P41">
-        <v>-199.5108937524415</v>
+        <v>-207.2268653871196</v>
       </c>
       <c r="Q41">
-        <v>-89.11089375244154</v>
+        <v>-96.82686538711957</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1151703754741942</v>
+        <v>0.1163265483987641</v>
       </c>
       <c r="T41">
-        <v>1.390436218497701</v>
+        <v>1.413610155472663</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.03370032726171642</v>
+        <v>0.03285781908017351</v>
       </c>
       <c r="W41">
-        <v>0.2278534628316873</v>
+        <v>0.2280521262608951</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.3370032726171642</v>
+        <v>0.3285781908017351</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1610167795436165</v>
+        <v>0.1629167795436165</v>
       </c>
       <c r="C42">
-        <v>-49.47748508130644</v>
+        <v>-107.3324109946923</v>
       </c>
       <c r="D42">
-        <v>1325.05700453852</v>
+        <v>1303.56044086563</v>
       </c>
       <c r="E42">
-        <v>1248.398265570261</v>
+        <v>1284.756627810756</v>
       </c>
       <c r="F42">
-        <v>1454.334489619826</v>
+        <v>1490.692851860322</v>
       </c>
       <c r="G42">
         <v>79.8</v>
@@ -4731,37 +4731,37 @@
         <v>112.68</v>
       </c>
       <c r="M42">
-        <v>342.9320726523551</v>
+        <v>351.5053744686639</v>
       </c>
       <c r="N42">
-        <v>-230.2520726523551</v>
+        <v>-238.8253744686639</v>
       </c>
       <c r="O42">
-        <v>-23.02520726523551</v>
+        <v>-23.88253744686639</v>
       </c>
       <c r="P42">
-        <v>-207.2268653871196</v>
+        <v>-214.9428370217975</v>
       </c>
       <c r="Q42">
-        <v>-96.82686538711957</v>
+        <v>-104.5428370217975</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1163265483987641</v>
+        <v>0.1175219136258618</v>
       </c>
       <c r="T42">
-        <v>1.413610155472663</v>
+        <v>1.437569649633216</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.03285781908017351</v>
+        <v>0.03205640885870586</v>
       </c>
       <c r="W42">
-        <v>0.2280521262608951</v>
+        <v>0.2282410987911172</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.3285781908017351</v>
+        <v>0.3205640885870586</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1629167795436165</v>
+        <v>0.1648167795436165</v>
       </c>
       <c r="C43">
-        <v>-107.3324109946923</v>
+        <v>-164.5009887959029</v>
       </c>
       <c r="D43">
-        <v>1303.56044086563</v>
+        <v>1282.750225304915</v>
       </c>
       <c r="E43">
-        <v>1284.756627810756</v>
+        <v>1321.114990051252</v>
       </c>
       <c r="F43">
-        <v>1490.692851860322</v>
+        <v>1527.051214100818</v>
       </c>
       <c r="G43">
         <v>79.8</v>
@@ -4813,37 +4813,37 @@
         <v>112.68</v>
       </c>
       <c r="M43">
-        <v>351.5053744686639</v>
+        <v>360.0786762849729</v>
       </c>
       <c r="N43">
-        <v>-238.8253744686639</v>
+        <v>-247.3986762849729</v>
       </c>
       <c r="O43">
-        <v>-23.88253744686639</v>
+        <v>-24.73986762849729</v>
       </c>
       <c r="P43">
-        <v>-214.9428370217975</v>
+        <v>-222.6588086564756</v>
       </c>
       <c r="Q43">
-        <v>-104.5428370217975</v>
+        <v>-112.2588086564756</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1175219136258618</v>
+        <v>0.1187584983435491</v>
       </c>
       <c r="T43">
-        <v>1.437569649633216</v>
+        <v>1.462355333247582</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.03205640885870586</v>
+        <v>0.03129316102873667</v>
       </c>
       <c r="W43">
-        <v>0.2282410987911172</v>
+        <v>0.2284210726294239</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.3205640885870586</v>
+        <v>0.3129316102873667</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1648167795436165</v>
+        <v>0.1667167795436165</v>
       </c>
       <c r="C44">
-        <v>-164.5009887959022</v>
+        <v>-221.0155728385193</v>
       </c>
       <c r="D44">
-        <v>1282.750225304915</v>
+        <v>1262.594003502794</v>
       </c>
       <c r="E44">
-        <v>1321.114990051252</v>
+        <v>1357.473352291748</v>
       </c>
       <c r="F44">
-        <v>1527.051214100818</v>
+        <v>1563.409576341313</v>
       </c>
       <c r="G44">
         <v>79.8</v>
@@ -4895,37 +4895,37 @@
         <v>112.68</v>
       </c>
       <c r="M44">
-        <v>360.0786762849728</v>
+        <v>368.6519781012817</v>
       </c>
       <c r="N44">
-        <v>-247.3986762849728</v>
+        <v>-255.9719781012817</v>
       </c>
       <c r="O44">
-        <v>-24.73986762849728</v>
+        <v>-25.59719781012817</v>
       </c>
       <c r="P44">
-        <v>-222.6588086564755</v>
+        <v>-230.3747802911535</v>
       </c>
       <c r="Q44">
-        <v>-112.2588086564755</v>
+        <v>-119.9747802911535</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.118758498343549</v>
+        <v>0.120038471998699</v>
       </c>
       <c r="T44">
-        <v>1.462355333247582</v>
+        <v>1.488010689971224</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.03129316102873668</v>
+        <v>0.03056541309783582</v>
       </c>
       <c r="W44">
-        <v>0.2284210726294239</v>
+        <v>0.2285926755915303</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.3129316102873668</v>
+        <v>0.3056541309783583</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1667167795436165</v>
+        <v>0.1686167795436165</v>
       </c>
       <c r="C45">
-        <v>-221.0155728385193</v>
+        <v>-276.9065153629929</v>
       </c>
       <c r="D45">
-        <v>1262.594003502794</v>
+        <v>1243.061423218816</v>
       </c>
       <c r="E45">
-        <v>1357.473352291748</v>
+        <v>1393.831714532243</v>
       </c>
       <c r="F45">
-        <v>1563.409576341313</v>
+        <v>1599.767938581809</v>
       </c>
       <c r="G45">
         <v>79.8</v>
@@ -4977,37 +4977,37 @@
         <v>112.68</v>
       </c>
       <c r="M45">
-        <v>368.6519781012817</v>
+        <v>377.2252799175906</v>
       </c>
       <c r="N45">
-        <v>-255.9719781012817</v>
+        <v>-264.5452799175906</v>
       </c>
       <c r="O45">
-        <v>-25.59719781012817</v>
+        <v>-26.45452799175906</v>
       </c>
       <c r="P45">
-        <v>-230.3747802911535</v>
+        <v>-238.0907519258315</v>
       </c>
       <c r="Q45">
-        <v>-119.9747802911535</v>
+        <v>-127.6907519258315</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.120038471998699</v>
+        <v>0.1213641589986758</v>
       </c>
       <c r="T45">
-        <v>1.488010689971224</v>
+        <v>1.514582309434996</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.03056541309783582</v>
+        <v>0.02987074461833956</v>
       </c>
       <c r="W45">
-        <v>0.2285926755915303</v>
+        <v>0.2287564784189955</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.3056541309783583</v>
+        <v>0.2987074461833955</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1686167795436165</v>
+        <v>0.1705167795436165</v>
       </c>
       <c r="C46">
-        <v>-276.9065153629929</v>
+        <v>-332.202319002781</v>
       </c>
       <c r="D46">
-        <v>1243.061423218816</v>
+        <v>1224.123981819524</v>
       </c>
       <c r="E46">
-        <v>1393.831714532243</v>
+        <v>1430.190076772739</v>
       </c>
       <c r="F46">
-        <v>1599.767938581809</v>
+        <v>1636.126300822305</v>
       </c>
       <c r="G46">
         <v>79.8</v>
@@ -5059,37 +5059,37 @@
         <v>112.68</v>
       </c>
       <c r="M46">
-        <v>377.2252799175906</v>
+        <v>385.7985817338994</v>
       </c>
       <c r="N46">
-        <v>-264.5452799175906</v>
+        <v>-273.1185817338994</v>
       </c>
       <c r="O46">
-        <v>-26.45452799175906</v>
+        <v>-27.31185817338994</v>
       </c>
       <c r="P46">
-        <v>-238.0907519258315</v>
+        <v>-245.8067235605095</v>
       </c>
       <c r="Q46">
-        <v>-127.6907519258315</v>
+        <v>-135.4067235605095</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1213641589986758</v>
+        <v>0.1227380527986517</v>
       </c>
       <c r="T46">
-        <v>1.514582309434996</v>
+        <v>1.542120169606541</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02987074461833956</v>
+        <v>0.02920695029348757</v>
       </c>
       <c r="W46">
-        <v>0.2287564784189955</v>
+        <v>0.2289130011207957</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2987074461833955</v>
+        <v>0.2920695029348757</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1705167795436165</v>
+        <v>0.1724167795436165</v>
       </c>
       <c r="C47">
-        <v>-332.202319002781</v>
+        <v>-386.9297755595317</v>
       </c>
       <c r="D47">
-        <v>1224.123981819524</v>
+        <v>1205.754887503269</v>
       </c>
       <c r="E47">
-        <v>1430.190076772739</v>
+        <v>1466.548439013235</v>
       </c>
       <c r="F47">
-        <v>1636.126300822305</v>
+        <v>1672.4846630628</v>
       </c>
       <c r="G47">
         <v>79.8</v>
@@ -5141,37 +5141,37 @@
         <v>112.68</v>
       </c>
       <c r="M47">
-        <v>385.7985817338994</v>
+        <v>394.3718835502083</v>
       </c>
       <c r="N47">
-        <v>-273.1185817338994</v>
+        <v>-281.6918835502083</v>
       </c>
       <c r="O47">
-        <v>-27.31185817338994</v>
+        <v>-28.16918835502084</v>
       </c>
       <c r="P47">
-        <v>-245.8067235605095</v>
+        <v>-253.5226951951875</v>
       </c>
       <c r="Q47">
-        <v>-135.4067235605095</v>
+        <v>-143.1226951951875</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1227380527986517</v>
+        <v>0.1241628315541823</v>
       </c>
       <c r="T47">
-        <v>1.542120169606541</v>
+        <v>1.570677950525181</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.02920695029348757</v>
+        <v>0.02857201659145522</v>
       </c>
       <c r="W47">
-        <v>0.2289130011207957</v>
+        <v>0.2290627184877349</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2920695029348757</v>
+        <v>0.2857201659145523</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1724167795436165</v>
+        <v>0.1743167795436165</v>
       </c>
       <c r="C48">
-        <v>-386.9297755595317</v>
+        <v>-441.1140924682945</v>
       </c>
       <c r="D48">
-        <v>1205.754887503269</v>
+        <v>1187.928932835001</v>
       </c>
       <c r="E48">
-        <v>1466.548439013235</v>
+        <v>1502.90680125373</v>
       </c>
       <c r="F48">
-        <v>1672.4846630628</v>
+        <v>1708.843025303296</v>
       </c>
       <c r="G48">
         <v>79.8</v>
@@ -5223,37 +5223,37 @@
         <v>112.68</v>
       </c>
       <c r="M48">
-        <v>394.3718835502083</v>
+        <v>402.9451853665172</v>
       </c>
       <c r="N48">
-        <v>-281.6918835502083</v>
+        <v>-290.2651853665172</v>
       </c>
       <c r="O48">
-        <v>-28.16918835502084</v>
+        <v>-29.02651853665172</v>
       </c>
       <c r="P48">
-        <v>-253.5226951951875</v>
+        <v>-261.2386668298655</v>
       </c>
       <c r="Q48">
-        <v>-143.1226951951875</v>
+        <v>-150.8386668298654</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1241628315541823</v>
+        <v>0.1256413755457707</v>
       </c>
       <c r="T48">
-        <v>1.570677950525181</v>
+        <v>1.600313383553958</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02857201659145522</v>
+        <v>0.02796410134482852</v>
       </c>
       <c r="W48">
-        <v>0.2290627184877349</v>
+        <v>0.2292060649028894</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2857201659145523</v>
+        <v>0.2796410134482852</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1743167795436165</v>
+        <v>0.1762167795436165</v>
       </c>
       <c r="C49">
-        <v>-441.1140924682945</v>
+        <v>-494.7790082081553</v>
       </c>
       <c r="D49">
-        <v>1187.928932835001</v>
+        <v>1170.622379335636</v>
       </c>
       <c r="E49">
-        <v>1502.90680125373</v>
+        <v>1539.265163494226</v>
       </c>
       <c r="F49">
-        <v>1708.843025303296</v>
+        <v>1745.201387543792</v>
       </c>
       <c r="G49">
         <v>79.8</v>
@@ -5305,37 +5305,37 @@
         <v>112.68</v>
       </c>
       <c r="M49">
-        <v>402.9451853665172</v>
+        <v>411.5184871828261</v>
       </c>
       <c r="N49">
-        <v>-290.2651853665172</v>
+        <v>-298.8384871828261</v>
       </c>
       <c r="O49">
-        <v>-29.02651853665172</v>
+        <v>-29.88384871828261</v>
       </c>
       <c r="P49">
-        <v>-261.2386668298655</v>
+        <v>-268.9546384645435</v>
       </c>
       <c r="Q49">
-        <v>-150.8386668298654</v>
+        <v>-158.5546384645435</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1256413755457707</v>
+        <v>0.1271767866139586</v>
       </c>
       <c r="T49">
-        <v>1.600313383553958</v>
+        <v>1.631088640929995</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02796410134482852</v>
+        <v>0.02738151590014459</v>
       </c>
       <c r="W49">
-        <v>0.2292060649028894</v>
+        <v>0.2293434385507459</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2796410134482852</v>
+        <v>0.2738151590014459</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1762167795436165</v>
+        <v>0.1781167795436165</v>
       </c>
       <c r="C50">
-        <v>-494.7790082081551</v>
+        <v>-547.9468977694435</v>
       </c>
       <c r="D50">
-        <v>1170.622379335636</v>
+        <v>1153.812852014844</v>
       </c>
       <c r="E50">
-        <v>1539.265163494226</v>
+        <v>1575.623525734722</v>
       </c>
       <c r="F50">
-        <v>1745.201387543791</v>
+        <v>1781.559749784287</v>
       </c>
       <c r="G50">
         <v>79.8</v>
@@ -5387,37 +5387,37 @@
         <v>112.68</v>
       </c>
       <c r="M50">
-        <v>411.518487182826</v>
+        <v>420.091788999135</v>
       </c>
       <c r="N50">
-        <v>-298.838487182826</v>
+        <v>-307.411788999135</v>
       </c>
       <c r="O50">
-        <v>-29.88384871828261</v>
+        <v>-30.7411788999135</v>
       </c>
       <c r="P50">
-        <v>-268.9546384645435</v>
+        <v>-276.6706100992214</v>
       </c>
       <c r="Q50">
-        <v>-158.5546384645434</v>
+        <v>-166.2706100992214</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1271767866139586</v>
+        <v>0.1287724098808989</v>
       </c>
       <c r="T50">
-        <v>1.631088640929995</v>
+        <v>1.663070771144309</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02738151590014459</v>
+        <v>0.02682270945320286</v>
       </c>
       <c r="W50">
-        <v>0.2293434385507459</v>
+        <v>0.2294752051109348</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2738151590014459</v>
+        <v>0.2682270945320286</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1781167795436165</v>
+        <v>0.1800167795436165</v>
       </c>
       <c r="C51">
-        <v>-547.9468977694435</v>
+        <v>-600.6388691628529</v>
       </c>
       <c r="D51">
-        <v>1153.812852014844</v>
+        <v>1137.47924286193</v>
       </c>
       <c r="E51">
-        <v>1575.623525734722</v>
+        <v>1611.981887975217</v>
       </c>
       <c r="F51">
-        <v>1781.559749784287</v>
+        <v>1817.918112024783</v>
       </c>
       <c r="G51">
         <v>79.8</v>
@@ -5469,37 +5469,37 @@
         <v>112.68</v>
       </c>
       <c r="M51">
-        <v>420.091788999135</v>
+        <v>428.6650908154438</v>
       </c>
       <c r="N51">
-        <v>-307.411788999135</v>
+        <v>-315.9850908154438</v>
       </c>
       <c r="O51">
-        <v>-30.7411788999135</v>
+        <v>-31.59850908154438</v>
       </c>
       <c r="P51">
-        <v>-276.6706100992214</v>
+        <v>-284.3865817338994</v>
       </c>
       <c r="Q51">
-        <v>-166.2706100992214</v>
+        <v>-173.9865817338994</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1287724098808989</v>
+        <v>0.1304318580785169</v>
       </c>
       <c r="T51">
-        <v>1.663070771144309</v>
+        <v>1.696332186567195</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02682270945320286</v>
+        <v>0.02628625526413881</v>
       </c>
       <c r="W51">
-        <v>0.2294752051109348</v>
+        <v>0.2296017010087161</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2682270945320286</v>
+        <v>0.2628625526413881</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1800167795436165</v>
+        <v>0.1819167795436165</v>
       </c>
       <c r="C52">
-        <v>-600.6388691628529</v>
+        <v>-652.8748518457651</v>
       </c>
       <c r="D52">
-        <v>1137.47924286193</v>
+        <v>1121.601622419513</v>
       </c>
       <c r="E52">
-        <v>1611.981887975217</v>
+        <v>1648.340250215713</v>
       </c>
       <c r="F52">
-        <v>1817.918112024783</v>
+        <v>1854.276474265278</v>
       </c>
       <c r="G52">
         <v>79.8</v>
@@ -5551,37 +5551,37 @@
         <v>112.68</v>
       </c>
       <c r="M52">
-        <v>428.6650908154438</v>
+        <v>437.2383926317527</v>
       </c>
       <c r="N52">
-        <v>-315.9850908154438</v>
+        <v>-324.5583926317527</v>
       </c>
       <c r="O52">
-        <v>-31.59850908154438</v>
+        <v>-32.45583926317527</v>
       </c>
       <c r="P52">
-        <v>-284.3865817338994</v>
+        <v>-292.1025533685774</v>
       </c>
       <c r="Q52">
-        <v>-173.9865817338994</v>
+        <v>-181.7025533685774</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1304318580785169</v>
+        <v>0.1321590388556295</v>
       </c>
       <c r="T52">
-        <v>1.696332186567195</v>
+        <v>1.730951210782852</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02628625526413881</v>
+        <v>0.02577083849425374</v>
       </c>
       <c r="W52">
-        <v>0.2296017010087161</v>
+        <v>0.229723236283055</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2628625526413881</v>
+        <v>0.2577083849425373</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1819167795436165</v>
+        <v>0.1838167795436165</v>
       </c>
       <c r="C53">
-        <v>-652.8748518457651</v>
+        <v>-704.6736778446809</v>
       </c>
       <c r="D53">
-        <v>1121.601622419513</v>
+        <v>1106.161158661093</v>
       </c>
       <c r="E53">
-        <v>1648.340250215713</v>
+        <v>1684.698612456209</v>
       </c>
       <c r="F53">
-        <v>1854.276474265278</v>
+        <v>1890.634836505774</v>
       </c>
       <c r="G53">
         <v>79.8</v>
@@ -5633,37 +5633,37 @@
         <v>112.68</v>
       </c>
       <c r="M53">
-        <v>437.2383926317527</v>
+        <v>445.8116944480616</v>
       </c>
       <c r="N53">
-        <v>-324.5583926317527</v>
+        <v>-333.1316944480616</v>
       </c>
       <c r="O53">
-        <v>-32.45583926317527</v>
+        <v>-33.31316944480616</v>
       </c>
       <c r="P53">
-        <v>-292.1025533685774</v>
+        <v>-299.8185250032554</v>
       </c>
       <c r="Q53">
-        <v>-181.7025533685774</v>
+        <v>-189.4185250032554</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1321590388556295</v>
+        <v>0.1339581854984551</v>
       </c>
       <c r="T53">
-        <v>1.730951210782852</v>
+        <v>1.767012694340828</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02577083849425374</v>
+        <v>0.02527524544628731</v>
       </c>
       <c r="W53">
-        <v>0.229723236283055</v>
+        <v>0.2298400971237655</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.2577083849425373</v>
+        <v>0.2527524544628732</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1838167795436165</v>
+        <v>0.1857167795436165</v>
       </c>
       <c r="C54">
-        <v>-704.6736778446809</v>
+        <v>-756.0531562680351</v>
       </c>
       <c r="D54">
-        <v>1106.161158661093</v>
+        <v>1091.140042478235</v>
       </c>
       <c r="E54">
-        <v>1684.698612456209</v>
+        <v>1721.056974696704</v>
       </c>
       <c r="F54">
-        <v>1890.634836505774</v>
+        <v>1926.99319874627</v>
       </c>
       <c r="G54">
         <v>79.8</v>
@@ -5715,37 +5715,37 @@
         <v>112.68</v>
       </c>
       <c r="M54">
-        <v>445.8116944480616</v>
+        <v>454.3849962643704</v>
       </c>
       <c r="N54">
-        <v>-333.1316944480616</v>
+        <v>-341.7049962643704</v>
       </c>
       <c r="O54">
-        <v>-33.31316944480616</v>
+        <v>-34.17049962643704</v>
       </c>
       <c r="P54">
-        <v>-299.8185250032554</v>
+        <v>-307.5344966379334</v>
       </c>
       <c r="Q54">
-        <v>-189.4185250032554</v>
+        <v>-197.1344966379334</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1339581854984551</v>
+        <v>0.1358338915728903</v>
       </c>
       <c r="T54">
-        <v>1.767012694340828</v>
+        <v>1.804608709114037</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02527524544628731</v>
+        <v>0.02479835402277246</v>
       </c>
       <c r="W54">
-        <v>0.2298400971237655</v>
+        <v>0.2299525481214303</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.2527524544628732</v>
+        <v>0.2479835402277246</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1857167795436165</v>
+        <v>0.1876167795436165</v>
       </c>
       <c r="C55">
-        <v>-756.0531562680351</v>
+        <v>-807.0301418292718</v>
       </c>
       <c r="D55">
-        <v>1091.140042478235</v>
+        <v>1076.521419157494</v>
       </c>
       <c r="E55">
-        <v>1721.056974696704</v>
+        <v>1757.4153369372</v>
       </c>
       <c r="F55">
-        <v>1926.99319874627</v>
+        <v>1963.351560986766</v>
       </c>
       <c r="G55">
         <v>79.8</v>
@@ -5797,37 +5797,37 @@
         <v>112.68</v>
       </c>
       <c r="M55">
-        <v>454.3849962643704</v>
+        <v>462.9582980806794</v>
       </c>
       <c r="N55">
-        <v>-341.7049962643704</v>
+        <v>-350.2782980806793</v>
       </c>
       <c r="O55">
-        <v>-34.17049962643704</v>
+        <v>-35.02782980806793</v>
       </c>
       <c r="P55">
-        <v>-307.5344966379334</v>
+        <v>-315.2504682726114</v>
       </c>
       <c r="Q55">
-        <v>-197.1344966379334</v>
+        <v>-204.8504682726114</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1358338915728903</v>
+        <v>0.1377911500853445</v>
       </c>
       <c r="T55">
-        <v>1.804608709114037</v>
+        <v>1.843839333225212</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02479835402277246</v>
+        <v>0.02433912524457297</v>
       </c>
       <c r="W55">
-        <v>0.2299525481214303</v>
+        <v>0.2300608342673297</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.2479835402277246</v>
+        <v>0.2433912524457297</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1876167795436165</v>
+        <v>0.1895167795436165</v>
       </c>
       <c r="C56">
-        <v>-807.0301418292718</v>
+        <v>-857.620597934482</v>
       </c>
       <c r="D56">
-        <v>1076.521419157494</v>
+        <v>1062.289325292779</v>
       </c>
       <c r="E56">
-        <v>1757.4153369372</v>
+        <v>1793.773699177696</v>
       </c>
       <c r="F56">
-        <v>1963.351560986766</v>
+        <v>1999.709923227261</v>
       </c>
       <c r="G56">
         <v>79.8</v>
@@ -5879,37 +5879,37 @@
         <v>112.68</v>
       </c>
       <c r="M56">
-        <v>462.9582980806794</v>
+        <v>471.5315998969882</v>
       </c>
       <c r="N56">
-        <v>-350.2782980806793</v>
+        <v>-358.8515998969882</v>
       </c>
       <c r="O56">
-        <v>-35.02782980806793</v>
+        <v>-35.88515998969882</v>
       </c>
       <c r="P56">
-        <v>-315.2504682726114</v>
+        <v>-322.9664399072894</v>
       </c>
       <c r="Q56">
-        <v>-204.8504682726114</v>
+        <v>-212.5664399072894</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1377911500853445</v>
+        <v>0.1398353978650188</v>
       </c>
       <c r="T56">
-        <v>1.843839333225212</v>
+        <v>1.884813540630217</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02433912524457297</v>
+        <v>0.02389659569467165</v>
       </c>
       <c r="W56">
-        <v>0.2300608342673297</v>
+        <v>0.2301651827351965</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.2433912524457297</v>
+        <v>0.2389659569467164</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1895167795436165</v>
+        <v>0.1914167795436165</v>
       </c>
       <c r="C57">
-        <v>-857.620597934482</v>
+        <v>-907.8396548310614</v>
       </c>
       <c r="D57">
-        <v>1062.289325292779</v>
+        <v>1048.428630636696</v>
       </c>
       <c r="E57">
-        <v>1793.773699177696</v>
+        <v>1830.132061418191</v>
       </c>
       <c r="F57">
-        <v>1999.709923227261</v>
+        <v>2036.068285467757</v>
       </c>
       <c r="G57">
         <v>79.8</v>
@@ -5961,37 +5961,37 @@
         <v>112.68</v>
       </c>
       <c r="M57">
-        <v>471.5315998969882</v>
+        <v>480.1049017132971</v>
       </c>
       <c r="N57">
-        <v>-358.8515998969882</v>
+        <v>-367.4249017132971</v>
       </c>
       <c r="O57">
-        <v>-35.88515998969882</v>
+        <v>-36.74249017132971</v>
       </c>
       <c r="P57">
-        <v>-322.9664399072894</v>
+        <v>-330.6824115419674</v>
       </c>
       <c r="Q57">
-        <v>-212.5664399072894</v>
+        <v>-220.2824115419674</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1398353978650188</v>
+        <v>0.1419725659983147</v>
       </c>
       <c r="T57">
-        <v>1.884813540630217</v>
+        <v>1.927650212008176</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.02389659569467165</v>
+        <v>0.02346987077155251</v>
       </c>
       <c r="W57">
-        <v>0.2301651827351965</v>
+        <v>0.2302658044720679</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.2389659569467164</v>
+        <v>0.234698707715525</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1914167795436165</v>
+        <v>0.1933167795436165</v>
       </c>
       <c r="C58">
-        <v>-907.8396548310614</v>
+        <v>-957.7016632626719</v>
       </c>
       <c r="D58">
-        <v>1048.428630636696</v>
+        <v>1034.924984445581</v>
       </c>
       <c r="E58">
-        <v>1830.132061418191</v>
+        <v>1866.490423658687</v>
       </c>
       <c r="F58">
-        <v>2036.068285467757</v>
+        <v>2072.426647708253</v>
       </c>
       <c r="G58">
         <v>79.8</v>
@@ -6043,37 +6043,37 @@
         <v>112.68</v>
       </c>
       <c r="M58">
-        <v>480.1049017132971</v>
+        <v>488.678203529606</v>
       </c>
       <c r="N58">
-        <v>-367.4249017132971</v>
+        <v>-375.998203529606</v>
       </c>
       <c r="O58">
-        <v>-36.74249017132971</v>
+        <v>-37.59982035296061</v>
       </c>
       <c r="P58">
-        <v>-330.6824115419674</v>
+        <v>-338.3983831766454</v>
       </c>
       <c r="Q58">
-        <v>-220.2824115419674</v>
+        <v>-227.9983831766454</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1419725659983147</v>
+        <v>0.1442091373006011</v>
       </c>
       <c r="T58">
-        <v>1.927650212008176</v>
+        <v>1.972479286706041</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.02346987077155251</v>
+        <v>0.02305811865275334</v>
       </c>
       <c r="W58">
-        <v>0.2302658044720679</v>
+        <v>0.2303628956216808</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.234698707715525</v>
+        <v>0.2305811865275333</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1933167795436165</v>
+        <v>0.1952167795436165</v>
       </c>
       <c r="C59">
-        <v>-957.7016632626719</v>
+        <v>-1007.220244030515</v>
       </c>
       <c r="D59">
-        <v>1034.924984445581</v>
+        <v>1021.764765918233</v>
       </c>
       <c r="E59">
-        <v>1866.490423658687</v>
+        <v>1902.848785899183</v>
       </c>
       <c r="F59">
-        <v>2072.426647708253</v>
+        <v>2108.785009948748</v>
       </c>
       <c r="G59">
         <v>79.8</v>
@@ -6125,37 +6125,37 @@
         <v>112.68</v>
       </c>
       <c r="M59">
-        <v>488.678203529606</v>
+        <v>497.2515053459148</v>
       </c>
       <c r="N59">
-        <v>-375.998203529606</v>
+        <v>-384.5715053459148</v>
       </c>
       <c r="O59">
-        <v>-37.59982035296061</v>
+        <v>-38.45715053459148</v>
       </c>
       <c r="P59">
-        <v>-338.3983831766454</v>
+        <v>-346.1143548113233</v>
       </c>
       <c r="Q59">
-        <v>-227.9983831766454</v>
+        <v>-235.7143548113233</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1442091373006011</v>
+        <v>0.1465522119982344</v>
       </c>
       <c r="T59">
-        <v>1.972479286706041</v>
+        <v>2.019443079246661</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.02305811865275334</v>
+        <v>0.02266056488287829</v>
       </c>
       <c r="W59">
-        <v>0.2303628956216808</v>
+        <v>0.2304566388006173</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.2305811865275333</v>
+        <v>0.2266056488287829</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1952167795436165</v>
+        <v>0.1971167795436165</v>
       </c>
       <c r="C60">
-        <v>-1007.220244030515</v>
+        <v>-1056.408333820724</v>
       </c>
       <c r="D60">
-        <v>1021.764765918233</v>
+        <v>1008.935038368519</v>
       </c>
       <c r="E60">
-        <v>1902.848785899183</v>
+        <v>1939.207148139678</v>
       </c>
       <c r="F60">
-        <v>2108.785009948748</v>
+        <v>2145.143372189244</v>
       </c>
       <c r="G60">
         <v>79.8</v>
@@ -6207,37 +6207,37 @@
         <v>112.68</v>
       </c>
       <c r="M60">
-        <v>497.2515053459148</v>
+        <v>505.8248071622236</v>
       </c>
       <c r="N60">
-        <v>-384.5715053459148</v>
+        <v>-393.1448071622236</v>
       </c>
       <c r="O60">
-        <v>-38.45715053459148</v>
+        <v>-39.31448071622236</v>
       </c>
       <c r="P60">
-        <v>-346.1143548113233</v>
+        <v>-353.8303264460013</v>
       </c>
       <c r="Q60">
-        <v>-235.7143548113233</v>
+        <v>-243.4303264460013</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1465522119982344</v>
+        <v>0.1490095830225816</v>
       </c>
       <c r="T60">
-        <v>2.019443079246661</v>
+        <v>2.068697788496579</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.02266056488287829</v>
+        <v>0.02227648751198204</v>
       </c>
       <c r="W60">
-        <v>0.2304566388006173</v>
+        <v>0.2305472042446746</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.2266056488287829</v>
+        <v>0.2227648751198205</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1971167795436165</v>
+        <v>0.1990167795436165</v>
       </c>
       <c r="C61">
-        <v>-1056.408333820724</v>
+        <v>-1105.278227621995</v>
       </c>
       <c r="D61">
-        <v>1008.935038368519</v>
+        <v>996.4235068077447</v>
       </c>
       <c r="E61">
-        <v>1939.207148139678</v>
+        <v>1975.565510380174</v>
       </c>
       <c r="F61">
-        <v>2145.143372189244</v>
+        <v>2181.501734429739</v>
       </c>
       <c r="G61">
         <v>79.8</v>
@@ -6289,37 +6289,37 @@
         <v>112.68</v>
       </c>
       <c r="M61">
-        <v>505.8248071622236</v>
+        <v>514.3981089785326</v>
       </c>
       <c r="N61">
-        <v>-393.1448071622236</v>
+        <v>-401.7181089785326</v>
       </c>
       <c r="O61">
-        <v>-39.31448071622236</v>
+        <v>-40.17181089785326</v>
       </c>
       <c r="P61">
-        <v>-353.8303264460013</v>
+        <v>-361.5462980806793</v>
       </c>
       <c r="Q61">
-        <v>-243.4303264460013</v>
+        <v>-251.1462980806793</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1490095830225816</v>
+        <v>0.1515898225981461</v>
       </c>
       <c r="T61">
-        <v>2.068697788496579</v>
+        <v>2.120415233208994</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.02227648751198204</v>
+        <v>0.02190521272011568</v>
       </c>
       <c r="W61">
-        <v>0.2305472042446746</v>
+        <v>0.2306347508405967</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.2227648751198205</v>
+        <v>0.2190521272011567</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1990167795436165</v>
+        <v>0.2009167795436165</v>
       </c>
       <c r="C62">
-        <v>-1105.278227621995</v>
+        <v>-1153.841618025819</v>
       </c>
       <c r="D62">
-        <v>996.4235068077447</v>
+        <v>984.2184786444158</v>
       </c>
       <c r="E62">
-        <v>1975.565510380174</v>
+        <v>2011.923872620669</v>
       </c>
       <c r="F62">
-        <v>2181.501734429739</v>
+        <v>2217.860096670235</v>
       </c>
       <c r="G62">
         <v>79.8</v>
@@ -6371,37 +6371,37 @@
         <v>112.68</v>
       </c>
       <c r="M62">
-        <v>514.3981089785326</v>
+        <v>522.9714107948415</v>
       </c>
       <c r="N62">
-        <v>-401.7181089785326</v>
+        <v>-410.2914107948415</v>
       </c>
       <c r="O62">
-        <v>-40.17181089785326</v>
+        <v>-41.02914107948416</v>
       </c>
       <c r="P62">
-        <v>-361.5462980806793</v>
+        <v>-369.2622697153574</v>
       </c>
       <c r="Q62">
-        <v>-251.1462980806793</v>
+        <v>-258.8622697153573</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1515898225981461</v>
+        <v>0.1543023821519448</v>
       </c>
       <c r="T62">
-        <v>2.120415233208994</v>
+        <v>2.174784854573327</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.02190521272011568</v>
+        <v>0.02154611087224492</v>
       </c>
       <c r="W62">
-        <v>0.2306347508405967</v>
+        <v>0.2307194270563247</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.2190521272011567</v>
+        <v>0.2154611087224493</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2009167795436165</v>
+        <v>0.2028167795436165</v>
       </c>
       <c r="C63">
-        <v>-1153.841618025819</v>
+        <v>-1202.10963167338</v>
       </c>
       <c r="D63">
-        <v>984.2184786444158</v>
+        <v>972.308827237351</v>
       </c>
       <c r="E63">
-        <v>2011.923872620669</v>
+        <v>2048.282234861165</v>
       </c>
       <c r="F63">
-        <v>2217.860096670235</v>
+        <v>2254.218458910731</v>
       </c>
       <c r="G63">
         <v>79.8</v>
@@ -6453,37 +6453,37 @@
         <v>112.68</v>
       </c>
       <c r="M63">
-        <v>522.9714107948415</v>
+        <v>531.5447126111504</v>
       </c>
       <c r="N63">
-        <v>-410.2914107948415</v>
+        <v>-418.8647126111504</v>
       </c>
       <c r="O63">
-        <v>-41.02914107948416</v>
+        <v>-41.88647126111505</v>
       </c>
       <c r="P63">
-        <v>-369.2622697153574</v>
+        <v>-376.9782413500354</v>
       </c>
       <c r="Q63">
-        <v>-258.8622697153573</v>
+        <v>-266.5782413500353</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1543023821519448</v>
+        <v>0.1571577079980486</v>
       </c>
       <c r="T63">
-        <v>2.174784854573327</v>
+        <v>2.232016034956836</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.02154611087224492</v>
+        <v>0.02119859295495065</v>
       </c>
       <c r="W63">
-        <v>0.2307194270563247</v>
+        <v>0.2308013717812226</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.2154611087224493</v>
+        <v>0.2119859295495065</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2028167795436165</v>
+        <v>0.2047167795436165</v>
       </c>
       <c r="C64">
-        <v>-1202.10963167338</v>
+        <v>-1250.092863087894</v>
       </c>
       <c r="D64">
-        <v>972.308827237351</v>
+        <v>960.6839580633324</v>
       </c>
       <c r="E64">
-        <v>2048.282234861165</v>
+        <v>2084.640597101661</v>
       </c>
       <c r="F64">
-        <v>2254.218458910731</v>
+        <v>2290.576821151226</v>
       </c>
       <c r="G64">
         <v>79.8</v>
@@ -6535,37 +6535,37 @@
         <v>112.68</v>
       </c>
       <c r="M64">
-        <v>531.5447126111504</v>
+        <v>540.1180144274592</v>
       </c>
       <c r="N64">
-        <v>-418.8647126111504</v>
+        <v>-427.4380144274592</v>
       </c>
       <c r="O64">
-        <v>-41.88647126111505</v>
+        <v>-42.74380144274593</v>
       </c>
       <c r="P64">
-        <v>-376.9782413500354</v>
+        <v>-384.6942129847133</v>
       </c>
       <c r="Q64">
-        <v>-266.5782413500353</v>
+        <v>-274.2942129847133</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1571577079980486</v>
+        <v>0.1601673757817796</v>
       </c>
       <c r="T64">
-        <v>2.232016034956836</v>
+        <v>2.292340792658372</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.02119859295495065</v>
+        <v>0.02086210735249112</v>
       </c>
       <c r="W64">
-        <v>0.2308013717812226</v>
+        <v>0.2308807150862826</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2119859295495065</v>
+        <v>0.2086210735249112</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2047167795436165</v>
+        <v>0.2066167795436165</v>
       </c>
       <c r="C65">
-        <v>-1250.092863087894</v>
+        <v>-1297.801406108657</v>
       </c>
       <c r="D65">
-        <v>960.6839580633324</v>
+        <v>949.3337772830655</v>
       </c>
       <c r="E65">
-        <v>2084.640597101661</v>
+        <v>2120.998959342156</v>
       </c>
       <c r="F65">
-        <v>2290.576821151226</v>
+        <v>2326.935183391722</v>
       </c>
       <c r="G65">
         <v>79.8</v>
@@ -6617,37 +6617,37 @@
         <v>112.68</v>
       </c>
       <c r="M65">
-        <v>540.1180144274592</v>
+        <v>548.6913162437681</v>
       </c>
       <c r="N65">
-        <v>-427.4380144274592</v>
+        <v>-436.0113162437681</v>
       </c>
       <c r="O65">
-        <v>-42.74380144274593</v>
+        <v>-43.60113162437682</v>
       </c>
       <c r="P65">
-        <v>-384.6942129847133</v>
+        <v>-392.4101846193913</v>
       </c>
       <c r="Q65">
-        <v>-274.2942129847133</v>
+        <v>-282.0101846193913</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1601673757817796</v>
+        <v>0.1633442473312735</v>
       </c>
       <c r="T65">
-        <v>2.292340792658372</v>
+        <v>2.356016925787771</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.02086210735249112</v>
+        <v>0.02053613692510844</v>
       </c>
       <c r="W65">
-        <v>0.2308807150862826</v>
+        <v>0.2309575789130594</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2086210735249112</v>
+        <v>0.2053613692510844</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2066167795436165</v>
+        <v>0.2085167795436165</v>
       </c>
       <c r="C66">
-        <v>-1297.801406108657</v>
+        <v>-1345.244883122791</v>
       </c>
       <c r="D66">
-        <v>949.3337772830655</v>
+        <v>938.2486625094269</v>
       </c>
       <c r="E66">
-        <v>2120.998959342156</v>
+        <v>2157.357321582652</v>
       </c>
       <c r="F66">
-        <v>2326.935183391722</v>
+        <v>2363.293545632218</v>
       </c>
       <c r="G66">
         <v>79.8</v>
@@ -6699,37 +6699,37 @@
         <v>112.68</v>
       </c>
       <c r="M66">
-        <v>548.6913162437681</v>
+        <v>557.2646180600771</v>
       </c>
       <c r="N66">
-        <v>-436.0113162437681</v>
+        <v>-444.584618060077</v>
       </c>
       <c r="O66">
-        <v>-43.60113162437682</v>
+        <v>-44.4584618060077</v>
       </c>
       <c r="P66">
-        <v>-392.4101846193913</v>
+        <v>-400.1261562540693</v>
       </c>
       <c r="Q66">
-        <v>-282.0101846193913</v>
+        <v>-289.7261562540693</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1633442473312735</v>
+        <v>0.1667026543978813</v>
       </c>
       <c r="T66">
-        <v>2.356016925787771</v>
+        <v>2.423331695095993</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.02053613692510844</v>
+        <v>0.02022019635702985</v>
       </c>
       <c r="W66">
-        <v>0.2309575789130594</v>
+        <v>0.2310320776990124</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2053613692510844</v>
+        <v>0.2022019635702985</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2085167795436165</v>
+        <v>0.2104167795436165</v>
       </c>
       <c r="C67">
-        <v>-1345.244883122791</v>
+        <v>-1392.432472272658</v>
       </c>
       <c r="D67">
-        <v>938.2486625094269</v>
+        <v>927.4194356000551</v>
       </c>
       <c r="E67">
-        <v>2157.357321582652</v>
+        <v>2193.715683823148</v>
       </c>
       <c r="F67">
-        <v>2363.293545632218</v>
+        <v>2399.651907872713</v>
       </c>
       <c r="G67">
         <v>79.8</v>
@@ -6781,37 +6781,37 @@
         <v>112.68</v>
       </c>
       <c r="M67">
-        <v>557.2646180600771</v>
+        <v>565.8379198763859</v>
       </c>
       <c r="N67">
-        <v>-444.584618060077</v>
+        <v>-453.1579198763858</v>
       </c>
       <c r="O67">
-        <v>-44.4584618060077</v>
+        <v>-45.31579198763859</v>
       </c>
       <c r="P67">
-        <v>-400.1261562540693</v>
+        <v>-407.8421278887473</v>
       </c>
       <c r="Q67">
-        <v>-289.7261562540693</v>
+        <v>-297.4421278887472</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1667026543978813</v>
+        <v>0.1702586148213484</v>
       </c>
       <c r="T67">
-        <v>2.423331695095993</v>
+        <v>2.494606156716463</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.02022019635702985</v>
+        <v>0.01991382974555971</v>
       </c>
       <c r="W67">
-        <v>0.2310320776990124</v>
+        <v>0.231104318945997</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2022019635702985</v>
+        <v>0.1991382974555971</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2104167795436165</v>
+        <v>0.2123167795436165</v>
       </c>
       <c r="C68">
-        <v>-1392.432472272658</v>
+        <v>-1439.372932800603</v>
       </c>
       <c r="D68">
-        <v>927.4194356000551</v>
+        <v>916.8373373126058</v>
       </c>
       <c r="E68">
-        <v>2193.715683823148</v>
+        <v>2230.074046063643</v>
       </c>
       <c r="F68">
-        <v>2399.651907872713</v>
+        <v>2436.010270113209</v>
       </c>
       <c r="G68">
         <v>79.8</v>
@@ -6863,37 +6863,37 @@
         <v>112.68</v>
       </c>
       <c r="M68">
-        <v>565.8379198763859</v>
+        <v>574.4112216926948</v>
       </c>
       <c r="N68">
-        <v>-453.1579198763858</v>
+        <v>-461.7312216926948</v>
       </c>
       <c r="O68">
-        <v>-45.31579198763859</v>
+        <v>-46.17312216926948</v>
       </c>
       <c r="P68">
-        <v>-407.8421278887473</v>
+        <v>-415.5580995234253</v>
       </c>
       <c r="Q68">
-        <v>-297.4421278887472</v>
+        <v>-305.1580995234253</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1702586148213484</v>
+        <v>0.1740300879977529</v>
       </c>
       <c r="T68">
-        <v>2.494606156716463</v>
+        <v>2.570200282677569</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01991382974555971</v>
+        <v>0.01961660840607374</v>
       </c>
       <c r="W68">
-        <v>0.231104318945997</v>
+        <v>0.2311744037378478</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1991382974555971</v>
+        <v>0.1961660840607373</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2123167795436165</v>
+        <v>0.2142167795436165</v>
       </c>
       <c r="C69">
-        <v>-1439.372932800603</v>
+        <v>-1486.074628678131</v>
       </c>
       <c r="D69">
-        <v>916.8373373126058</v>
+        <v>906.4940036755738</v>
       </c>
       <c r="E69">
-        <v>2230.074046063643</v>
+        <v>2266.432408304139</v>
       </c>
       <c r="F69">
-        <v>2436.010270113209</v>
+        <v>2472.368632353705</v>
       </c>
       <c r="G69">
         <v>79.8</v>
@@ -6945,37 +6945,37 @@
         <v>112.68</v>
       </c>
       <c r="M69">
-        <v>574.4112216926948</v>
+        <v>582.9845235090037</v>
       </c>
       <c r="N69">
-        <v>-461.7312216926948</v>
+        <v>-470.3045235090037</v>
       </c>
       <c r="O69">
-        <v>-46.17312216926948</v>
+        <v>-47.03045235090037</v>
       </c>
       <c r="P69">
-        <v>-415.5580995234253</v>
+        <v>-423.2740711581033</v>
       </c>
       <c r="Q69">
-        <v>-305.1580995234253</v>
+        <v>-312.8740711581033</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1740300879977529</v>
+        <v>0.1780372782476827</v>
       </c>
       <c r="T69">
-        <v>2.570200282677569</v>
+        <v>2.650519041511243</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01961660840607374</v>
+        <v>0.0193281288706903</v>
       </c>
       <c r="W69">
-        <v>0.2311744037378478</v>
+        <v>0.2312424272122912</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1961660840607373</v>
+        <v>0.193281288706903</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2142167795436165</v>
+        <v>0.2161167795436165</v>
       </c>
       <c r="C70">
-        <v>-1486.074628678131</v>
+        <v>-1532.545550653486</v>
       </c>
       <c r="D70">
-        <v>906.4940036755738</v>
+        <v>896.381443940715</v>
       </c>
       <c r="E70">
-        <v>2266.432408304139</v>
+        <v>2302.790770544635</v>
       </c>
       <c r="F70">
-        <v>2472.368632353705</v>
+        <v>2508.726994594201</v>
       </c>
       <c r="G70">
         <v>79.8</v>
@@ -7027,37 +7027,37 @@
         <v>112.68</v>
       </c>
       <c r="M70">
-        <v>582.9845235090037</v>
+        <v>591.5578253253126</v>
       </c>
       <c r="N70">
-        <v>-470.3045235090037</v>
+        <v>-478.8778253253126</v>
       </c>
       <c r="O70">
-        <v>-47.03045235090037</v>
+        <v>-47.88778253253126</v>
       </c>
       <c r="P70">
-        <v>-423.2740711581033</v>
+        <v>-430.9900427927813</v>
       </c>
       <c r="Q70">
-        <v>-312.8740711581033</v>
+        <v>-320.5900427927813</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1780372782476827</v>
+        <v>0.1823029969008338</v>
       </c>
       <c r="T70">
-        <v>2.650519041511243</v>
+        <v>2.736019655753541</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.0193281288706903</v>
+        <v>0.01904801106097015</v>
       </c>
       <c r="W70">
-        <v>0.2312424272122912</v>
+        <v>0.2313084789918233</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.193281288706903</v>
+        <v>0.1904801106097015</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2161167795436165</v>
+        <v>0.2180167795436165</v>
       </c>
       <c r="C71">
-        <v>-1532.545550653486</v>
+        <v>-1578.793336839782</v>
       </c>
       <c r="D71">
-        <v>896.381443940715</v>
+        <v>886.4920199949141</v>
       </c>
       <c r="E71">
-        <v>2302.790770544635</v>
+        <v>2339.14913278513</v>
       </c>
       <c r="F71">
-        <v>2508.726994594201</v>
+        <v>2545.085356834696</v>
       </c>
       <c r="G71">
         <v>79.8</v>
@@ -7109,37 +7109,37 @@
         <v>112.68</v>
       </c>
       <c r="M71">
-        <v>591.5578253253126</v>
+        <v>600.1311271416214</v>
       </c>
       <c r="N71">
-        <v>-478.8778253253126</v>
+        <v>-487.4511271416214</v>
       </c>
       <c r="O71">
-        <v>-47.88778253253126</v>
+        <v>-48.74511271416214</v>
       </c>
       <c r="P71">
-        <v>-430.9900427927813</v>
+        <v>-438.7060144274593</v>
       </c>
       <c r="Q71">
-        <v>-320.5900427927813</v>
+        <v>-328.3060144274592</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1823029969008338</v>
+        <v>0.1868530967975282</v>
       </c>
       <c r="T71">
-        <v>2.736019655753541</v>
+        <v>2.827220310945326</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.01904801106097015</v>
+        <v>0.01877589661724201</v>
       </c>
       <c r="W71">
-        <v>0.2313084789918233</v>
+        <v>0.2313726435776544</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1904801106097015</v>
+        <v>0.18775896617242</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2180167795436165</v>
+        <v>0.2199167795436165</v>
       </c>
       <c r="C72">
-        <v>-1578.793336839782</v>
+        <v>-1624.825291955158</v>
       </c>
       <c r="D72">
-        <v>886.4920199949141</v>
+        <v>876.8184271200337</v>
       </c>
       <c r="E72">
-        <v>2339.14913278513</v>
+        <v>2375.507495025626</v>
       </c>
       <c r="F72">
-        <v>2545.085356834696</v>
+        <v>2581.443719075192</v>
       </c>
       <c r="G72">
         <v>79.8</v>
@@ -7191,37 +7191,37 @@
         <v>112.68</v>
       </c>
       <c r="M72">
-        <v>600.1311271416214</v>
+        <v>608.7044289579303</v>
       </c>
       <c r="N72">
-        <v>-487.4511271416214</v>
+        <v>-496.0244289579303</v>
       </c>
       <c r="O72">
-        <v>-48.74511271416214</v>
+        <v>-49.60244289579303</v>
       </c>
       <c r="P72">
-        <v>-438.7060144274593</v>
+        <v>-446.4219860621373</v>
       </c>
       <c r="Q72">
-        <v>-328.3060144274592</v>
+        <v>-336.0219860621372</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1868530967975282</v>
+        <v>0.1917169966870982</v>
       </c>
       <c r="T72">
-        <v>2.827220310945326</v>
+        <v>2.924710666495165</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01877589661724201</v>
+        <v>0.01851144736911184</v>
       </c>
       <c r="W72">
-        <v>0.2313726435776544</v>
+        <v>0.2314350007103634</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.18775896617242</v>
+        <v>0.1851144736911183</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2199167795436165</v>
+        <v>0.2218167795436165</v>
       </c>
       <c r="C73">
-        <v>-1624.825291955158</v>
+        <v>-1670.648405316811</v>
       </c>
       <c r="D73">
-        <v>876.8184271200337</v>
+        <v>867.3536759988757</v>
       </c>
       <c r="E73">
-        <v>2375.507495025626</v>
+        <v>2411.865857266122</v>
       </c>
       <c r="F73">
-        <v>2581.443719075191</v>
+        <v>2617.802081315687</v>
       </c>
       <c r="G73">
         <v>79.8</v>
@@ -7273,37 +7273,37 @@
         <v>112.68</v>
       </c>
       <c r="M73">
-        <v>608.7044289579302</v>
+        <v>617.2777307742391</v>
       </c>
       <c r="N73">
-        <v>-496.0244289579302</v>
+        <v>-504.5977307742391</v>
       </c>
       <c r="O73">
-        <v>-49.60244289579302</v>
+        <v>-50.45977307742391</v>
       </c>
       <c r="P73">
-        <v>-446.4219860621372</v>
+        <v>-454.1379576968152</v>
       </c>
       <c r="Q73">
-        <v>-336.0219860621372</v>
+        <v>-343.7379576968152</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1917169966870981</v>
+        <v>0.1969283179973516</v>
       </c>
       <c r="T73">
-        <v>2.924710666495164</v>
+        <v>3.029164618869991</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01851144736911184</v>
+        <v>0.01825434393342973</v>
       </c>
       <c r="W73">
-        <v>0.2314350007103634</v>
+        <v>0.2314956257004973</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1851144736911183</v>
+        <v>0.1825434393342973</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2218167795436165</v>
+        <v>0.2237167795436165</v>
       </c>
       <c r="C74">
-        <v>-1670.648405316811</v>
+        <v>-1716.269367682069</v>
       </c>
       <c r="D74">
-        <v>867.3536759988757</v>
+        <v>858.0910758741143</v>
       </c>
       <c r="E74">
-        <v>2411.865857266122</v>
+        <v>2448.224219506617</v>
       </c>
       <c r="F74">
-        <v>2617.802081315687</v>
+        <v>2654.160443556183</v>
       </c>
       <c r="G74">
         <v>79.8</v>
@@ -7355,37 +7355,37 @@
         <v>112.68</v>
       </c>
       <c r="M74">
-        <v>617.2777307742391</v>
+        <v>625.851032590548</v>
       </c>
       <c r="N74">
-        <v>-504.5977307742391</v>
+        <v>-513.1710325905481</v>
       </c>
       <c r="O74">
-        <v>-50.45977307742391</v>
+        <v>-51.31710325905481</v>
       </c>
       <c r="P74">
-        <v>-454.1379576968152</v>
+        <v>-461.8539293314932</v>
       </c>
       <c r="Q74">
-        <v>-343.7379576968152</v>
+        <v>-351.4539293314932</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1969283179973516</v>
+        <v>0.2025256631083646</v>
       </c>
       <c r="T74">
-        <v>3.029164618869991</v>
+        <v>3.141355901050361</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01825434393342973</v>
+        <v>0.01800428442749234</v>
       </c>
       <c r="W74">
-        <v>0.2314956257004973</v>
+        <v>0.2315545897319973</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1825434393342973</v>
+        <v>0.1800428442749232</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2237167795436165</v>
+        <v>0.2256167795436165</v>
       </c>
       <c r="C75">
-        <v>-1716.269367682069</v>
+        <v>-1761.694587021767</v>
       </c>
       <c r="D75">
-        <v>858.0910758741143</v>
+        <v>849.0242187749117</v>
       </c>
       <c r="E75">
-        <v>2448.224219506617</v>
+        <v>2484.582581747113</v>
       </c>
       <c r="F75">
-        <v>2654.160443556183</v>
+        <v>2690.518805796679</v>
       </c>
       <c r="G75">
         <v>79.8</v>
@@ -7437,37 +7437,37 @@
         <v>112.68</v>
       </c>
       <c r="M75">
-        <v>625.851032590548</v>
+        <v>634.4243344068569</v>
       </c>
       <c r="N75">
-        <v>-513.1710325905481</v>
+        <v>-521.744334406857</v>
       </c>
       <c r="O75">
-        <v>-51.31710325905481</v>
+        <v>-52.1744334406857</v>
       </c>
       <c r="P75">
-        <v>-461.8539293314932</v>
+        <v>-469.5699009661713</v>
       </c>
       <c r="Q75">
-        <v>-351.4539293314932</v>
+        <v>-359.1699009661713</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2025256631083646</v>
+        <v>0.2085535732279171</v>
       </c>
       <c r="T75">
-        <v>3.141355901050361</v>
+        <v>3.26217728185999</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01800428442749234</v>
+        <v>0.01776098328658027</v>
       </c>
       <c r="W75">
-        <v>0.2315545897319973</v>
+        <v>0.2316119601410244</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1800428442749232</v>
+        <v>0.1776098328658027</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2256167795436165</v>
+        <v>0.2275167795436165</v>
       </c>
       <c r="C76">
-        <v>-1761.694587021767</v>
+        <v>-1806.930203304095</v>
       </c>
       <c r="D76">
-        <v>849.0242187749117</v>
+        <v>840.1469647330788</v>
       </c>
       <c r="E76">
-        <v>2484.582581747113</v>
+        <v>2520.940943987609</v>
       </c>
       <c r="F76">
-        <v>2690.518805796679</v>
+        <v>2726.877168037174</v>
       </c>
       <c r="G76">
         <v>79.8</v>
@@ -7519,37 +7519,37 @@
         <v>112.68</v>
       </c>
       <c r="M76">
-        <v>634.4243344068569</v>
+        <v>642.9976362231657</v>
       </c>
       <c r="N76">
-        <v>-521.744334406857</v>
+        <v>-530.3176362231657</v>
       </c>
       <c r="O76">
-        <v>-52.1744334406857</v>
+        <v>-53.03176362231657</v>
       </c>
       <c r="P76">
-        <v>-469.5699009661713</v>
+        <v>-477.2858726008491</v>
       </c>
       <c r="Q76">
-        <v>-359.1699009661713</v>
+        <v>-366.8858726008491</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2085535732279171</v>
+        <v>0.2150637161570338</v>
       </c>
       <c r="T76">
-        <v>3.26217728185999</v>
+        <v>3.39266437313439</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01776098328658027</v>
+        <v>0.01752417017609254</v>
       </c>
       <c r="W76">
-        <v>0.2316119601410244</v>
+        <v>0.2316678006724774</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1776098328658027</v>
+        <v>0.1752417017609255</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2275167795436165</v>
+        <v>0.2294167795436165</v>
       </c>
       <c r="C77">
-        <v>-1806.930203304095</v>
+        <v>-1851.982102360564</v>
       </c>
       <c r="D77">
-        <v>840.1469647330788</v>
+        <v>831.4534279171058</v>
       </c>
       <c r="E77">
-        <v>2520.940943987609</v>
+        <v>2557.299306228104</v>
       </c>
       <c r="F77">
-        <v>2726.877168037174</v>
+        <v>2763.23553027767</v>
       </c>
       <c r="G77">
         <v>79.8</v>
@@ -7601,37 +7601,37 @@
         <v>112.68</v>
       </c>
       <c r="M77">
-        <v>642.9976362231657</v>
+        <v>651.5709380394746</v>
       </c>
       <c r="N77">
-        <v>-530.3176362231657</v>
+        <v>-538.8909380394746</v>
       </c>
       <c r="O77">
-        <v>-53.03176362231657</v>
+        <v>-53.88909380394746</v>
       </c>
       <c r="P77">
-        <v>-477.2858726008491</v>
+        <v>-485.0018442355271</v>
       </c>
       <c r="Q77">
-        <v>-366.8858726008491</v>
+        <v>-374.6018442355271</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2150637161570338</v>
+        <v>0.2221163709969103</v>
       </c>
       <c r="T77">
-        <v>3.39266437313439</v>
+        <v>3.534025388681657</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01752417017609254</v>
+        <v>0.017293588989565</v>
       </c>
       <c r="W77">
-        <v>0.2316678006724774</v>
+        <v>0.2317221717162606</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1752417017609255</v>
+        <v>0.1729358898956501</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2294167795436165</v>
+        <v>0.2313167795436165</v>
       </c>
       <c r="C78">
-        <v>-1851.982102360564</v>
+        <v>-1896.855928899916</v>
       </c>
       <c r="D78">
-        <v>831.4534279171058</v>
+        <v>822.9379636182498</v>
       </c>
       <c r="E78">
-        <v>2557.299306228104</v>
+        <v>2593.6576684686</v>
       </c>
       <c r="F78">
-        <v>2763.23553027767</v>
+        <v>2799.593892518166</v>
       </c>
       <c r="G78">
         <v>79.8</v>
@@ -7683,37 +7683,37 @@
         <v>112.68</v>
       </c>
       <c r="M78">
-        <v>651.5709380394746</v>
+        <v>660.1442398557836</v>
       </c>
       <c r="N78">
-        <v>-538.8909380394746</v>
+        <v>-547.4642398557835</v>
       </c>
       <c r="O78">
-        <v>-53.88909380394746</v>
+        <v>-54.74642398557835</v>
       </c>
       <c r="P78">
-        <v>-485.0018442355271</v>
+        <v>-492.7178158702051</v>
       </c>
       <c r="Q78">
-        <v>-374.6018442355271</v>
+        <v>-382.3178158702051</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2221163709969103</v>
+        <v>0.229782300170689</v>
       </c>
       <c r="T78">
-        <v>3.534025388681657</v>
+        <v>3.687678666450425</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.017293588989565</v>
+        <v>0.01706899692476546</v>
       </c>
       <c r="W78">
-        <v>0.2317221717162606</v>
+        <v>0.2317751305251403</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1729358898956501</v>
+        <v>0.1706899692476547</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2313167795436165</v>
+        <v>0.2332167795436165</v>
       </c>
       <c r="C79">
-        <v>-1896.855928899916</v>
+        <v>-1941.557098730438</v>
       </c>
       <c r="D79">
-        <v>822.9379636182498</v>
+        <v>814.5951560282235</v>
       </c>
       <c r="E79">
-        <v>2593.6576684686</v>
+        <v>2630.016030709096</v>
       </c>
       <c r="F79">
-        <v>2799.593892518166</v>
+        <v>2835.952254758661</v>
       </c>
       <c r="G79">
         <v>79.8</v>
@@ -7765,37 +7765,37 @@
         <v>112.68</v>
       </c>
       <c r="M79">
-        <v>660.1442398557836</v>
+        <v>668.7175416720924</v>
       </c>
       <c r="N79">
-        <v>-547.4642398557835</v>
+        <v>-556.0375416720924</v>
       </c>
       <c r="O79">
-        <v>-54.74642398557835</v>
+        <v>-55.60375416720925</v>
       </c>
       <c r="P79">
-        <v>-492.7178158702051</v>
+        <v>-500.4337875048832</v>
       </c>
       <c r="Q79">
-        <v>-382.3178158702051</v>
+        <v>-390.0337875048832</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.229782300170689</v>
+        <v>0.2381451319966293</v>
       </c>
       <c r="T79">
-        <v>3.687678666450425</v>
+        <v>3.855300424016353</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01706899692476546</v>
+        <v>0.01685016363085821</v>
       </c>
       <c r="W79">
-        <v>0.2317751305251403</v>
+        <v>0.2318267314158436</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1706899692476547</v>
+        <v>0.1685016363085821</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2332167795436165</v>
+        <v>0.2351167795436165</v>
       </c>
       <c r="C80">
-        <v>-1941.557098730438</v>
+        <v>-1986.090810246284</v>
       </c>
       <c r="D80">
-        <v>814.5951560282235</v>
+        <v>806.4198067528733</v>
       </c>
       <c r="E80">
-        <v>2630.016030709096</v>
+        <v>2666.374392949591</v>
       </c>
       <c r="F80">
-        <v>2835.952254758661</v>
+        <v>2872.310616999157</v>
       </c>
       <c r="G80">
         <v>79.8</v>
@@ -7847,37 +7847,37 @@
         <v>112.68</v>
       </c>
       <c r="M80">
-        <v>668.7175416720924</v>
+        <v>677.2908434884013</v>
       </c>
       <c r="N80">
-        <v>-556.0375416720924</v>
+        <v>-564.6108434884013</v>
       </c>
       <c r="O80">
-        <v>-55.60375416720925</v>
+        <v>-56.46108434884013</v>
       </c>
       <c r="P80">
-        <v>-500.4337875048832</v>
+        <v>-508.1497591395612</v>
       </c>
       <c r="Q80">
-        <v>-390.0337875048832</v>
+        <v>-397.7497591395612</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2381451319966293</v>
+        <v>0.2473044239964688</v>
       </c>
       <c r="T80">
-        <v>3.855300424016353</v>
+        <v>4.038886158493322</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01685016363085821</v>
+        <v>0.01663687042034102</v>
       </c>
       <c r="W80">
-        <v>0.2318267314158436</v>
+        <v>0.2318770259548836</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1685016363085821</v>
+        <v>0.1663687042034101</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2351167795436165</v>
+        <v>0.2370167795436165</v>
       </c>
       <c r="C81">
-        <v>-1986.090810246284</v>
+        <v>-2030.462055229013</v>
       </c>
       <c r="D81">
-        <v>806.4198067528733</v>
+        <v>798.4069240106396</v>
       </c>
       <c r="E81">
-        <v>2666.374392949591</v>
+        <v>2702.732755190087</v>
       </c>
       <c r="F81">
-        <v>2872.310616999157</v>
+        <v>2908.668979239653</v>
       </c>
       <c r="G81">
         <v>79.8</v>
@@ -7929,37 +7929,37 @@
         <v>112.68</v>
       </c>
       <c r="M81">
-        <v>677.2908434884013</v>
+        <v>685.8641453047102</v>
       </c>
       <c r="N81">
-        <v>-564.6108434884013</v>
+        <v>-573.1841453047102</v>
       </c>
       <c r="O81">
-        <v>-56.46108434884013</v>
+        <v>-57.31841453047102</v>
       </c>
       <c r="P81">
-        <v>-508.1497591395612</v>
+        <v>-515.8657307742392</v>
       </c>
       <c r="Q81">
-        <v>-397.7497591395612</v>
+        <v>-405.4657307742392</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2473044239964688</v>
+        <v>0.2573796451962923</v>
       </c>
       <c r="T81">
-        <v>4.038886158493322</v>
+        <v>4.240830466417989</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01663687042034102</v>
+        <v>0.01642890954008676</v>
       </c>
       <c r="W81">
-        <v>0.2318770259548836</v>
+        <v>0.2319260631304475</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1663687042034101</v>
+        <v>0.1642890954008674</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2370167795436165</v>
+        <v>0.2389167795436165</v>
       </c>
       <c r="C82">
-        <v>-2030.462055229013</v>
+        <v>-2074.675629011484</v>
       </c>
       <c r="D82">
-        <v>798.4069240106396</v>
+        <v>790.5517124686643</v>
       </c>
       <c r="E82">
-        <v>2702.732755190087</v>
+        <v>2739.091117430583</v>
       </c>
       <c r="F82">
-        <v>2908.668979239653</v>
+        <v>2945.027341480149</v>
       </c>
       <c r="G82">
         <v>79.8</v>
@@ -8011,37 +8011,37 @@
         <v>112.68</v>
       </c>
       <c r="M82">
-        <v>685.8641453047102</v>
+        <v>694.4374471210191</v>
       </c>
       <c r="N82">
-        <v>-573.1841453047102</v>
+        <v>-581.7574471210191</v>
       </c>
       <c r="O82">
-        <v>-57.31841453047102</v>
+        <v>-58.17574471210192</v>
       </c>
       <c r="P82">
-        <v>-515.8657307742392</v>
+        <v>-523.5817024089172</v>
       </c>
       <c r="Q82">
-        <v>-405.4657307742392</v>
+        <v>-413.1817024089172</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2573796451962923</v>
+        <v>0.2685154159960971</v>
       </c>
       <c r="T82">
-        <v>4.240830466417989</v>
+        <v>4.464032069913672</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01642890954008676</v>
+        <v>0.01622608349638198</v>
       </c>
       <c r="W82">
-        <v>0.2319260631304475</v>
+        <v>0.2319738895115531</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1642890954008674</v>
+        <v>0.1622608349638197</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2389167795436165</v>
+        <v>0.2408167795436165</v>
       </c>
       <c r="C83">
-        <v>-2074.675629011484</v>
+        <v>-2118.736140047615</v>
       </c>
       <c r="D83">
-        <v>790.5517124686643</v>
+        <v>782.8495636730295</v>
       </c>
       <c r="E83">
-        <v>2739.091117430583</v>
+        <v>2775.449479671078</v>
       </c>
       <c r="F83">
-        <v>2945.027341480149</v>
+        <v>2981.385703720644</v>
       </c>
       <c r="G83">
         <v>79.8</v>
@@ -8093,37 +8093,37 @@
         <v>112.68</v>
       </c>
       <c r="M83">
-        <v>694.4374471210191</v>
+        <v>703.0107489373279</v>
       </c>
       <c r="N83">
-        <v>-581.7574471210191</v>
+        <v>-590.3307489373278</v>
       </c>
       <c r="O83">
-        <v>-58.17574471210192</v>
+        <v>-59.03307489373279</v>
       </c>
       <c r="P83">
-        <v>-523.5817024089172</v>
+        <v>-531.2976740435951</v>
       </c>
       <c r="Q83">
-        <v>-413.1817024089172</v>
+        <v>-420.8976740435951</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2685154159960971</v>
+        <v>0.280888494662547</v>
       </c>
       <c r="T83">
-        <v>4.464032069913672</v>
+        <v>4.712033851575543</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01622608349638198</v>
+        <v>0.01602820442935293</v>
       </c>
       <c r="W83">
-        <v>0.2319738895115531</v>
+        <v>0.2320205493955586</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1622608349638197</v>
+        <v>0.1602820442935294</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2408167795436165</v>
+        <v>0.2427167795436165</v>
       </c>
       <c r="C84">
-        <v>-2118.736140047615</v>
+        <v>-2162.648018928115</v>
       </c>
       <c r="D84">
-        <v>782.8495636730295</v>
+        <v>775.2960470330249</v>
       </c>
       <c r="E84">
-        <v>2775.449479671078</v>
+        <v>2811.807841911574</v>
       </c>
       <c r="F84">
-        <v>2981.385703720644</v>
+        <v>3017.74406596114</v>
       </c>
       <c r="G84">
         <v>79.8</v>
@@ -8175,37 +8175,37 @@
         <v>112.68</v>
       </c>
       <c r="M84">
-        <v>703.0107489373279</v>
+        <v>711.5840507536368</v>
       </c>
       <c r="N84">
-        <v>-590.3307489373278</v>
+        <v>-598.9040507536367</v>
       </c>
       <c r="O84">
-        <v>-59.03307489373279</v>
+        <v>-59.89040507536367</v>
       </c>
       <c r="P84">
-        <v>-531.2976740435951</v>
+        <v>-539.0136456782731</v>
       </c>
       <c r="Q84">
-        <v>-420.8976740435951</v>
+        <v>-428.6136456782731</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.280888494662547</v>
+        <v>0.2947172296426969</v>
       </c>
       <c r="T84">
-        <v>4.712033851575543</v>
+        <v>4.989212313432929</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01602820442935293</v>
+        <v>0.01583509353261374</v>
       </c>
       <c r="W84">
-        <v>0.2320205493955586</v>
+        <v>0.2320660849450097</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1602820442935294</v>
+        <v>0.1583509353261374</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2427167795436165</v>
+        <v>0.2446167795436165</v>
       </c>
       <c r="C85">
-        <v>-2162.648018928115</v>
+        <v>-2206.41552687927</v>
       </c>
       <c r="D85">
-        <v>775.2960470330249</v>
+        <v>767.8869013223652</v>
       </c>
       <c r="E85">
-        <v>2811.807841911574</v>
+        <v>2848.16620415207</v>
       </c>
       <c r="F85">
-        <v>3017.74406596114</v>
+        <v>3054.102428201636</v>
       </c>
       <c r="G85">
         <v>79.8</v>
@@ -8257,37 +8257,37 @@
         <v>112.68</v>
       </c>
       <c r="M85">
-        <v>711.5840507536368</v>
+        <v>720.1573525699457</v>
       </c>
       <c r="N85">
-        <v>-598.9040507536367</v>
+        <v>-607.4773525699457</v>
       </c>
       <c r="O85">
-        <v>-59.89040507536367</v>
+        <v>-60.74773525699457</v>
       </c>
       <c r="P85">
-        <v>-539.0136456782731</v>
+        <v>-546.7296173129511</v>
       </c>
       <c r="Q85">
-        <v>-428.6136456782731</v>
+        <v>-436.3296173129511</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2947172296426969</v>
+        <v>0.3102745564953655</v>
       </c>
       <c r="T85">
-        <v>4.989212313432929</v>
+        <v>5.301038083022488</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01583509353261374</v>
+        <v>0.01564658051436834</v>
       </c>
       <c r="W85">
-        <v>0.2320660849450097</v>
+        <v>0.232110536314712</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1583509353261374</v>
+        <v>0.1564658051436835</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2446167795436165</v>
+        <v>0.2465167795436165</v>
       </c>
       <c r="C86">
-        <v>-2206.41552687927</v>
+        <v>-2250.042763779024</v>
       </c>
       <c r="D86">
-        <v>767.8869013223649</v>
+        <v>760.6180266631073</v>
       </c>
       <c r="E86">
-        <v>2848.166204152069</v>
+        <v>2884.524566392565</v>
       </c>
       <c r="F86">
-        <v>3054.102428201635</v>
+        <v>3090.460790442131</v>
       </c>
       <c r="G86">
         <v>79.8</v>
@@ -8339,37 +8339,37 @@
         <v>112.68</v>
       </c>
       <c r="M86">
-        <v>720.1573525699456</v>
+        <v>728.7306543862545</v>
       </c>
       <c r="N86">
-        <v>-607.4773525699457</v>
+        <v>-616.0506543862546</v>
       </c>
       <c r="O86">
-        <v>-60.74773525699457</v>
+        <v>-61.60506543862546</v>
       </c>
       <c r="P86">
-        <v>-546.7296173129511</v>
+        <v>-554.4455889476291</v>
       </c>
       <c r="Q86">
-        <v>-436.3296173129511</v>
+        <v>-444.0455889476291</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3102745564953653</v>
+        <v>0.3279061935950563</v>
       </c>
       <c r="T86">
-        <v>5.301038083022484</v>
+        <v>5.654440621890649</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01564658051436834</v>
+        <v>0.01546250309655224</v>
       </c>
       <c r="W86">
-        <v>0.232110536314712</v>
+        <v>0.232153941769833</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1564658051436834</v>
+        <v>0.1546250309655223</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2465167795436165</v>
+        <v>0.2484167795436165</v>
       </c>
       <c r="C87">
-        <v>-2250.042763779024</v>
+        <v>-2293.533675722042</v>
       </c>
       <c r="D87">
-        <v>760.6180266631073</v>
+        <v>753.4854769605848</v>
       </c>
       <c r="E87">
-        <v>2884.524566392565</v>
+        <v>2920.882928633061</v>
       </c>
       <c r="F87">
-        <v>3090.460790442131</v>
+        <v>3126.819152682627</v>
       </c>
       <c r="G87">
         <v>79.8</v>
@@ -8421,37 +8421,37 @@
         <v>112.68</v>
       </c>
       <c r="M87">
-        <v>728.7306543862545</v>
+        <v>737.3039562025634</v>
       </c>
       <c r="N87">
-        <v>-616.0506543862546</v>
+        <v>-624.6239562025635</v>
       </c>
       <c r="O87">
-        <v>-61.60506543862546</v>
+        <v>-62.46239562025635</v>
       </c>
       <c r="P87">
-        <v>-554.4455889476291</v>
+        <v>-562.1615605823072</v>
       </c>
       <c r="Q87">
-        <v>-444.0455889476291</v>
+        <v>-451.7615605823072</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3279061935950563</v>
+        <v>0.3480566359947032</v>
       </c>
       <c r="T87">
-        <v>5.654440621890649</v>
+        <v>6.058329237739982</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01546250309655224</v>
+        <v>0.01528270654891791</v>
       </c>
       <c r="W87">
-        <v>0.232153941769833</v>
+        <v>0.2321963377957652</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1546250309655223</v>
+        <v>0.152827065489179</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2484167795436165</v>
+        <v>0.2503167795436165</v>
       </c>
       <c r="C88">
-        <v>-2293.533675722042</v>
+        <v>-2336.892062163094</v>
       </c>
       <c r="D88">
-        <v>753.4854769605848</v>
+        <v>746.4854527600282</v>
       </c>
       <c r="E88">
-        <v>2920.882928633061</v>
+        <v>2957.241290873556</v>
       </c>
       <c r="F88">
-        <v>3126.819152682627</v>
+        <v>3163.177514923122</v>
       </c>
       <c r="G88">
         <v>79.8</v>
@@ -8503,37 +8503,37 @@
         <v>112.68</v>
       </c>
       <c r="M88">
-        <v>737.3039562025634</v>
+        <v>745.8772580188722</v>
       </c>
       <c r="N88">
-        <v>-624.6239562025635</v>
+        <v>-633.1972580188722</v>
       </c>
       <c r="O88">
-        <v>-62.46239562025635</v>
+        <v>-63.31972580188722</v>
       </c>
       <c r="P88">
-        <v>-562.1615605823072</v>
+        <v>-569.8775322169849</v>
       </c>
       <c r="Q88">
-        <v>-451.7615605823072</v>
+        <v>-459.477532216985</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3480566359947032</v>
+        <v>0.3713071464558342</v>
       </c>
       <c r="T88">
-        <v>6.058329237739982</v>
+        <v>6.524354563719981</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01528270654891791</v>
+        <v>0.01510704325525219</v>
       </c>
       <c r="W88">
-        <v>0.2321963377957652</v>
+        <v>0.2322377592004116</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.152827065489179</v>
+        <v>0.1510704325525219</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2503167795436165</v>
+        <v>0.2522167795436165</v>
       </c>
       <c r="C89">
-        <v>-2336.892062163094</v>
+        <v>-2380.121582665917</v>
       </c>
       <c r="D89">
-        <v>746.4854527600282</v>
+        <v>739.6142944977009</v>
       </c>
       <c r="E89">
-        <v>2957.241290873556</v>
+        <v>2993.599653114052</v>
       </c>
       <c r="F89">
-        <v>3163.177514923122</v>
+        <v>3199.535877163618</v>
       </c>
       <c r="G89">
         <v>79.8</v>
@@ -8585,37 +8585,37 @@
         <v>112.68</v>
       </c>
       <c r="M89">
-        <v>745.8772580188722</v>
+        <v>754.4505598351811</v>
       </c>
       <c r="N89">
-        <v>-633.1972580188722</v>
+        <v>-641.7705598351811</v>
       </c>
       <c r="O89">
-        <v>-63.31972580188722</v>
+        <v>-64.17705598351812</v>
       </c>
       <c r="P89">
-        <v>-569.8775322169849</v>
+        <v>-577.5935038516629</v>
       </c>
       <c r="Q89">
-        <v>-459.477532216985</v>
+        <v>-467.193503851663</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3713071464558342</v>
+        <v>0.3984327419938205</v>
       </c>
       <c r="T89">
-        <v>6.524354563719981</v>
+        <v>7.068050777363314</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01510704325525219</v>
+        <v>0.01493537230916978</v>
       </c>
       <c r="W89">
-        <v>0.2322377592004116</v>
+        <v>0.2322782392094978</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1510704325525219</v>
+        <v>0.1493537230916978</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2522167795436165</v>
+        <v>0.2541167795436165</v>
       </c>
       <c r="C90">
-        <v>-2380.121582665917</v>
+        <v>-2423.225763282754</v>
       </c>
       <c r="D90">
-        <v>739.6142944977009</v>
+        <v>732.8684761213597</v>
       </c>
       <c r="E90">
-        <v>2993.599653114052</v>
+        <v>3029.958015354548</v>
       </c>
       <c r="F90">
-        <v>3199.535877163618</v>
+        <v>3235.894239404114</v>
       </c>
       <c r="G90">
         <v>79.8</v>
@@ -8667,37 +8667,37 @@
         <v>112.68</v>
       </c>
       <c r="M90">
-        <v>754.4505598351811</v>
+        <v>763.0238616514901</v>
       </c>
       <c r="N90">
-        <v>-641.7705598351811</v>
+        <v>-650.34386165149</v>
       </c>
       <c r="O90">
-        <v>-64.17705598351812</v>
+        <v>-65.034386165149</v>
       </c>
       <c r="P90">
-        <v>-577.5935038516629</v>
+        <v>-585.3094754863409</v>
       </c>
       <c r="Q90">
-        <v>-467.193503851663</v>
+        <v>-474.909475486341</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3984327419938205</v>
+        <v>0.4304902639932587</v>
       </c>
       <c r="T90">
-        <v>7.068050777363314</v>
+        <v>7.710600848032706</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01493537230916978</v>
+        <v>0.01476755913715663</v>
       </c>
       <c r="W90">
-        <v>0.2322782392094978</v>
+        <v>0.2323178095554585</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1493537230916978</v>
+        <v>0.1476755913715664</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2541167795436165</v>
+        <v>0.2560167795436165</v>
       </c>
       <c r="C91">
-        <v>-2423.225763282754</v>
+        <v>-2466.208002587933</v>
       </c>
       <c r="D91">
-        <v>732.8684761213597</v>
+        <v>726.2445990566763</v>
       </c>
       <c r="E91">
-        <v>3029.958015354548</v>
+        <v>3066.316377595043</v>
       </c>
       <c r="F91">
-        <v>3235.894239404114</v>
+        <v>3272.252601644609</v>
       </c>
       <c r="G91">
         <v>79.8</v>
@@ -8749,37 +8749,37 @@
         <v>112.68</v>
       </c>
       <c r="M91">
-        <v>763.0238616514901</v>
+        <v>771.5971634677989</v>
       </c>
       <c r="N91">
-        <v>-650.34386165149</v>
+        <v>-658.9171634677989</v>
       </c>
       <c r="O91">
-        <v>-65.034386165149</v>
+        <v>-65.89171634677989</v>
       </c>
       <c r="P91">
-        <v>-585.3094754863409</v>
+        <v>-593.0254471210191</v>
       </c>
       <c r="Q91">
-        <v>-474.909475486341</v>
+        <v>-482.6254471210191</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4304902639932587</v>
+        <v>0.4689592903925846</v>
       </c>
       <c r="T91">
-        <v>7.710600848032706</v>
+        <v>8.481660932835977</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01476755913715663</v>
+        <v>0.01460347514674378</v>
       </c>
       <c r="W91">
-        <v>0.2323178095554585</v>
+        <v>0.2323565005603978</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1476755913715664</v>
+        <v>0.1460347514674377</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2560167795436165</v>
+        <v>0.2579167795436165</v>
       </c>
       <c r="C92">
-        <v>-2466.208002587933</v>
+        <v>-2509.071577387173</v>
       </c>
       <c r="D92">
-        <v>726.2445990566763</v>
+        <v>719.7393864979314</v>
       </c>
       <c r="E92">
-        <v>3066.316377595043</v>
+        <v>3102.674739835539</v>
       </c>
       <c r="F92">
-        <v>3272.252601644609</v>
+        <v>3308.610963885105</v>
       </c>
       <c r="G92">
         <v>79.8</v>
@@ -8831,37 +8831,37 @@
         <v>112.68</v>
       </c>
       <c r="M92">
-        <v>771.5971634677989</v>
+        <v>780.1704652841078</v>
       </c>
       <c r="N92">
-        <v>-658.9171634677989</v>
+        <v>-667.4904652841078</v>
       </c>
       <c r="O92">
-        <v>-65.89171634677989</v>
+        <v>-66.74904652841079</v>
       </c>
       <c r="P92">
-        <v>-593.0254471210191</v>
+        <v>-600.7414187556971</v>
       </c>
       <c r="Q92">
-        <v>-482.6254471210191</v>
+        <v>-490.3414187556971</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4689592903925846</v>
+        <v>0.5159769893250941</v>
       </c>
       <c r="T92">
-        <v>8.481660932835977</v>
+        <v>9.424067703151087</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01460347514674378</v>
+        <v>0.01444299739787847</v>
       </c>
       <c r="W92">
-        <v>0.2323565005603978</v>
+        <v>0.2323943412135803</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1460347514674377</v>
+        <v>0.1444299739787845</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2579167795436165</v>
+        <v>0.2598167795436165</v>
       </c>
       <c r="C93">
-        <v>-2509.071577387173</v>
+        <v>-2551.819648122781</v>
       </c>
       <c r="D93">
-        <v>719.7393864979314</v>
+        <v>713.3496780028202</v>
       </c>
       <c r="E93">
-        <v>3102.674739835539</v>
+        <v>3139.033102076035</v>
       </c>
       <c r="F93">
-        <v>3308.610963885105</v>
+        <v>3344.969326125601</v>
       </c>
       <c r="G93">
         <v>79.8</v>
@@ -8913,37 +8913,37 @@
         <v>112.68</v>
       </c>
       <c r="M93">
-        <v>780.1704652841078</v>
+        <v>788.7437671004167</v>
       </c>
       <c r="N93">
-        <v>-667.4904652841078</v>
+        <v>-676.0637671004167</v>
       </c>
       <c r="O93">
-        <v>-66.74904652841079</v>
+        <v>-67.60637671004167</v>
       </c>
       <c r="P93">
-        <v>-600.7414187556971</v>
+        <v>-608.4573903903751</v>
       </c>
       <c r="Q93">
-        <v>-490.3414187556971</v>
+        <v>-498.0573903903751</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5159769893250941</v>
+        <v>0.5747491129907309</v>
       </c>
       <c r="T93">
-        <v>9.424067703151087</v>
+        <v>10.60207616604498</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01444299739787847</v>
+        <v>0.01428600829572761</v>
       </c>
       <c r="W93">
-        <v>0.2323943412135803</v>
+        <v>0.2324313592438675</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1444299739787845</v>
+        <v>0.142860082957276</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2598167795436165</v>
+        <v>0.2617167795436165</v>
       </c>
       <c r="C94">
-        <v>-2551.819648122781</v>
+        <v>-2594.455263993449</v>
       </c>
       <c r="D94">
-        <v>713.3496780028202</v>
+        <v>707.0724243726477</v>
       </c>
       <c r="E94">
-        <v>3139.033102076035</v>
+        <v>3175.391464316531</v>
       </c>
       <c r="F94">
-        <v>3344.969326125601</v>
+        <v>3381.327688366096</v>
       </c>
       <c r="G94">
         <v>79.8</v>
@@ -8995,37 +8995,37 @@
         <v>112.68</v>
       </c>
       <c r="M94">
-        <v>788.7437671004167</v>
+        <v>797.3170689167256</v>
       </c>
       <c r="N94">
-        <v>-676.0637671004167</v>
+        <v>-684.6370689167256</v>
       </c>
       <c r="O94">
-        <v>-67.60637671004167</v>
+        <v>-68.46370689167257</v>
       </c>
       <c r="P94">
-        <v>-608.4573903903751</v>
+        <v>-616.1733620250531</v>
       </c>
       <c r="Q94">
-        <v>-498.0573903903751</v>
+        <v>-505.7733620250531</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5747491129907309</v>
+        <v>0.6503132719894068</v>
       </c>
       <c r="T94">
-        <v>10.60207616604498</v>
+        <v>12.11665847547997</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01428600829572761</v>
+        <v>0.01413239530330043</v>
       </c>
       <c r="W94">
-        <v>0.2324313592438675</v>
+        <v>0.2324675811874818</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.142860082957276</v>
+        <v>0.1413239530330043</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2617167795436165</v>
+        <v>0.2636167795436165</v>
       </c>
       <c r="C95">
-        <v>-2594.455263993449</v>
+        <v>-2636.981367806117</v>
       </c>
       <c r="D95">
-        <v>707.0724243726477</v>
+        <v>700.9046828004746</v>
       </c>
       <c r="E95">
-        <v>3175.391464316531</v>
+        <v>3211.749826557026</v>
       </c>
       <c r="F95">
-        <v>3381.327688366096</v>
+        <v>3417.686050606592</v>
       </c>
       <c r="G95">
         <v>79.8</v>
@@ -9077,37 +9077,37 @@
         <v>112.68</v>
       </c>
       <c r="M95">
-        <v>797.3170689167256</v>
+        <v>805.8903707330344</v>
       </c>
       <c r="N95">
-        <v>-684.6370689167256</v>
+        <v>-693.2103707330343</v>
       </c>
       <c r="O95">
-        <v>-68.46370689167257</v>
+        <v>-69.32103707330343</v>
       </c>
       <c r="P95">
-        <v>-616.1733620250531</v>
+        <v>-623.8893336597309</v>
       </c>
       <c r="Q95">
-        <v>-505.7733620250531</v>
+        <v>-513.489333659731</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6503132719894068</v>
+        <v>0.7510654839876415</v>
       </c>
       <c r="T95">
-        <v>12.11665847547997</v>
+        <v>14.13610155472664</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.01413239530330043</v>
+        <v>0.01398205067241426</v>
       </c>
       <c r="W95">
-        <v>0.2324675811874818</v>
+        <v>0.2325030324514447</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1413239530330043</v>
+        <v>0.1398205067241427</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2636167795436165</v>
+        <v>0.2655167795436165</v>
       </c>
       <c r="C96">
-        <v>-2636.981367806117</v>
+        <v>-2679.400800576079</v>
       </c>
       <c r="D96">
-        <v>700.9046828004746</v>
+        <v>694.8436122710091</v>
       </c>
       <c r="E96">
-        <v>3211.749826557026</v>
+        <v>3248.108188797522</v>
       </c>
       <c r="F96">
-        <v>3417.686050606592</v>
+        <v>3454.044412847088</v>
       </c>
       <c r="G96">
         <v>79.8</v>
@@ -9159,37 +9159,37 @@
         <v>112.68</v>
       </c>
       <c r="M96">
-        <v>805.8903707330344</v>
+        <v>814.4636725493433</v>
       </c>
       <c r="N96">
-        <v>-693.2103707330343</v>
+        <v>-701.7836725493432</v>
       </c>
       <c r="O96">
-        <v>-69.32103707330343</v>
+        <v>-70.17836725493433</v>
       </c>
       <c r="P96">
-        <v>-623.8893336597309</v>
+        <v>-631.6053052944089</v>
       </c>
       <c r="Q96">
-        <v>-513.489333659731</v>
+        <v>-521.205305294409</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7510654839876415</v>
+        <v>0.8921185807851703</v>
       </c>
       <c r="T96">
-        <v>14.13610155472664</v>
+        <v>16.96332186567198</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01398205067241426</v>
+        <v>0.01383487119165201</v>
       </c>
       <c r="W96">
-        <v>0.2325030324514447</v>
+        <v>0.2325377373730085</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1398205067241427</v>
+        <v>0.1383487119165201</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2655167795436165</v>
+        <v>0.2674167795436165</v>
       </c>
       <c r="C97">
-        <v>-2679.400800576079</v>
+        <v>-2721.716305890459</v>
       </c>
       <c r="D97">
-        <v>694.8436122710091</v>
+        <v>688.8864691971241</v>
       </c>
       <c r="E97">
-        <v>3248.108188797522</v>
+        <v>3284.466551038018</v>
       </c>
       <c r="F97">
-        <v>3454.044412847088</v>
+        <v>3490.402775087583</v>
       </c>
       <c r="G97">
         <v>79.8</v>
@@ -9241,37 +9241,37 @@
         <v>112.68</v>
       </c>
       <c r="M97">
-        <v>814.4636725493433</v>
+        <v>823.0369743656522</v>
       </c>
       <c r="N97">
-        <v>-701.7836725493432</v>
+        <v>-710.3569743656521</v>
       </c>
       <c r="O97">
-        <v>-70.17836725493433</v>
+        <v>-71.03569743656521</v>
       </c>
       <c r="P97">
-        <v>-631.6053052944089</v>
+        <v>-639.3212769290869</v>
       </c>
       <c r="Q97">
-        <v>-521.205305294409</v>
+        <v>-528.921276929087</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8921185807851703</v>
+        <v>1.103698225981463</v>
       </c>
       <c r="T97">
-        <v>16.96332186567198</v>
+        <v>21.20415233208998</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01383487119165201</v>
+        <v>0.01369075795007229</v>
       </c>
       <c r="W97">
-        <v>0.2325377373730085</v>
+        <v>0.232571719275373</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1383487119165201</v>
+        <v>0.136907579500723</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2674167795436165</v>
+        <v>0.2693167795436165</v>
       </c>
       <c r="C98">
-        <v>-2721.716305890459</v>
+        <v>-2763.930534049151</v>
       </c>
       <c r="D98">
-        <v>688.8864691971241</v>
+        <v>683.0306032789277</v>
       </c>
       <c r="E98">
-        <v>3284.466551038017</v>
+        <v>3320.824913278513</v>
       </c>
       <c r="F98">
-        <v>3490.402775087583</v>
+        <v>3526.761137328079</v>
       </c>
       <c r="G98">
         <v>79.8</v>
@@ -9323,37 +9323,37 @@
         <v>112.68</v>
       </c>
       <c r="M98">
-        <v>823.0369743656521</v>
+        <v>831.610276181961</v>
       </c>
       <c r="N98">
-        <v>-710.3569743656521</v>
+        <v>-718.9302761819611</v>
       </c>
       <c r="O98">
-        <v>-71.03569743656521</v>
+        <v>-71.89302761819611</v>
       </c>
       <c r="P98">
-        <v>-639.3212769290869</v>
+        <v>-647.0372485637649</v>
       </c>
       <c r="Q98">
-        <v>-528.921276929087</v>
+        <v>-536.637248563765</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.103698225981461</v>
+        <v>1.456330967975281</v>
       </c>
       <c r="T98">
-        <v>21.20415233208992</v>
+        <v>28.27220310945323</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.0136907579500723</v>
+        <v>0.01354961611553547</v>
       </c>
       <c r="W98">
-        <v>0.232571719275373</v>
+        <v>0.2326050005199567</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1369075795007229</v>
+        <v>0.1354961611553546</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2693167795436165</v>
+        <v>0.2712167795436164</v>
       </c>
       <c r="C99">
-        <v>-2763.930534049151</v>
+        <v>-2806.046045996326</v>
       </c>
       <c r="D99">
-        <v>683.0306032789277</v>
+        <v>677.273453572249</v>
       </c>
       <c r="E99">
-        <v>3320.824913278513</v>
+        <v>3357.183275519009</v>
       </c>
       <c r="F99">
-        <v>3526.761137328079</v>
+        <v>3563.119499568575</v>
       </c>
       <c r="G99">
         <v>79.8</v>
@@ -9405,37 +9405,37 @@
         <v>112.68</v>
       </c>
       <c r="M99">
-        <v>831.610276181961</v>
+        <v>840.1835779982699</v>
       </c>
       <c r="N99">
-        <v>-718.9302761819611</v>
+        <v>-727.50357799827</v>
       </c>
       <c r="O99">
-        <v>-71.89302761819611</v>
+        <v>-72.750357799827</v>
       </c>
       <c r="P99">
-        <v>-647.0372485637649</v>
+        <v>-654.7532201984429</v>
       </c>
       <c r="Q99">
-        <v>-536.637248563765</v>
+        <v>-544.353220198443</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.456330967975281</v>
+        <v>2.161596451962921</v>
       </c>
       <c r="T99">
-        <v>28.27220310945323</v>
+        <v>42.40830466417984</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01354961611553547</v>
+        <v>0.01341135472660143</v>
       </c>
       <c r="W99">
-        <v>0.2326050005199567</v>
+        <v>0.2326376025554674</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1354961611553546</v>
+        <v>0.1341135472660142</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2712167795436164</v>
+        <v>0.2731167795436165</v>
       </c>
       <c r="C100">
-        <v>-2806.046045996326</v>
+        <v>-2848.065317054774</v>
       </c>
       <c r="D100">
-        <v>677.273453572249</v>
+        <v>671.6125447542955</v>
       </c>
       <c r="E100">
-        <v>3357.183275519009</v>
+        <v>3393.541637759504</v>
       </c>
       <c r="F100">
-        <v>3563.119499568575</v>
+        <v>3599.47786180907</v>
       </c>
       <c r="G100">
         <v>79.8</v>
@@ -9487,37 +9487,37 @@
         <v>112.68</v>
       </c>
       <c r="M100">
-        <v>840.1835779982699</v>
+        <v>848.7568798145787</v>
       </c>
       <c r="N100">
-        <v>-727.50357799827</v>
+        <v>-736.0768798145787</v>
       </c>
       <c r="O100">
-        <v>-72.750357799827</v>
+        <v>-73.60768798145787</v>
       </c>
       <c r="P100">
-        <v>-654.7532201984429</v>
+        <v>-662.4691918331208</v>
       </c>
       <c r="Q100">
-        <v>-544.353220198443</v>
+        <v>-552.0691918331208</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.161596451962921</v>
+        <v>4.277392903925842</v>
       </c>
       <c r="T100">
-        <v>42.40830466417984</v>
+        <v>84.81660932835969</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01341135472660143</v>
+        <v>0.01327588649703981</v>
       </c>
       <c r="W100">
-        <v>0.2326376025554674</v>
+        <v>0.232669545963998</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1341135472660142</v>
+        <v>0.1327588649703981</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2731167795436165</v>
-      </c>
-      <c r="C101">
-        <v>-2848.065317054774</v>
-      </c>
-      <c r="D101">
-        <v>671.6125447542955</v>
-      </c>
-      <c r="E101">
-        <v>3393.541637759504</v>
-      </c>
-      <c r="F101">
-        <v>3599.47786180907</v>
-      </c>
-      <c r="G101">
-        <v>79.8</v>
-      </c>
-      <c r="H101">
-        <v>3429.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>223.08</v>
-      </c>
-      <c r="K101">
-        <v>110.4</v>
-      </c>
-      <c r="L101">
-        <v>112.68</v>
-      </c>
-      <c r="M101">
-        <v>848.7568798145787</v>
-      </c>
-      <c r="N101">
-        <v>-736.0768798145787</v>
-      </c>
-      <c r="O101">
-        <v>-73.60768798145787</v>
-      </c>
-      <c r="P101">
-        <v>-662.4691918331208</v>
-      </c>
-      <c r="Q101">
-        <v>-552.0691918331208</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.277392903925842</v>
-      </c>
-      <c r="T101">
-        <v>84.81660932835969</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01327588649703981</v>
-      </c>
-      <c r="W101">
-        <v>0.232669545963998</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1327588649703981</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
